--- a/data/stx_xlsx/BILIa.ST.xlsx
+++ b/data/stx_xlsx/BILIa.ST.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="490">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="491">
   <si>
     <t>Company Fundamentals - Income Statement</t>
   </si>
@@ -967,6 +967,9 @@
   </si>
   <si>
     <t>Bank loans</t>
+  </si>
+  <si>
+    <t>Bond issue (Do not use)</t>
   </si>
   <si>
     <t>Other non-current liabilities</t>
@@ -1614,7 +1617,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1692,6 +1695,9 @@
     </xf>
     <xf borderId="3" fillId="0" fontId="8" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -16889,8 +16895,8 @@
       <c r="W145" s="15"/>
     </row>
     <row r="146" ht="15.0" customHeight="1">
-      <c r="A146" s="14" t="s">
-        <v>283</v>
+      <c r="A146" s="26" t="s">
+        <v>316</v>
       </c>
       <c r="B146" s="18">
         <v>1741.89</v>
@@ -16955,7 +16961,7 @@
     </row>
     <row r="147" ht="15.0" customHeight="1">
       <c r="A147" s="14" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B147" s="18">
         <v>1293.57</v>
@@ -17020,7 +17026,7 @@
     </row>
     <row r="148" ht="15.0" customHeight="1">
       <c r="A148" s="14" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B148" s="15"/>
       <c r="C148" s="18">
@@ -17061,7 +17067,7 @@
     </row>
     <row r="149" ht="15.0" customHeight="1">
       <c r="A149" s="14" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B149" s="15"/>
       <c r="C149" s="19">
@@ -17090,7 +17096,7 @@
     </row>
     <row r="150" ht="15.0" customHeight="1">
       <c r="A150" s="14" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B150" s="15"/>
       <c r="C150" s="19">
@@ -17119,7 +17125,7 @@
     </row>
     <row r="151" ht="15.0" customHeight="1">
       <c r="A151" s="14" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B151" s="15"/>
       <c r="C151" s="15"/>
@@ -17176,7 +17182,7 @@
     </row>
     <row r="152" ht="15.0" customHeight="1">
       <c r="A152" s="14" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B152" s="15"/>
       <c r="C152" s="18">
@@ -17274,7 +17280,7 @@
     </row>
     <row r="154" ht="15.0" customHeight="1">
       <c r="A154" s="14" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B154" s="18">
         <v>521.58</v>
@@ -17345,7 +17351,7 @@
     </row>
     <row r="155" ht="15.0" customHeight="1">
       <c r="A155" s="14" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B155" s="21">
         <v>-1.09</v>
@@ -17376,7 +17382,7 @@
     </row>
     <row r="156" ht="15.0" customHeight="1">
       <c r="A156" s="16" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B156" s="20">
         <v>9763.56</v>
@@ -17447,7 +17453,7 @@
     </row>
     <row r="157" ht="15.0" customHeight="1">
       <c r="A157" s="14" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B157" s="15"/>
       <c r="C157" s="15"/>
@@ -17476,7 +17482,7 @@
     </row>
     <row r="158" ht="15.0" customHeight="1">
       <c r="A158" s="16" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B158" s="17">
         <v>16648.03</v>
@@ -17547,7 +17553,7 @@
     </row>
     <row r="159" ht="15.0" customHeight="1">
       <c r="A159" s="14" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B159" s="15"/>
       <c r="C159" s="18">
@@ -17616,7 +17622,7 @@
     </row>
     <row r="160" ht="15.0" customHeight="1">
       <c r="A160" s="14" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B160" s="15"/>
       <c r="C160" s="18">
@@ -17675,7 +17681,7 @@
     </row>
     <row r="161" ht="15.0" customHeight="1">
       <c r="A161" s="14" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B161" s="15"/>
       <c r="C161" s="15"/>
@@ -17706,7 +17712,7 @@
     </row>
     <row r="162" ht="15.0" customHeight="1">
       <c r="A162" s="14" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B162" s="15"/>
       <c r="C162" s="15"/>
@@ -17737,7 +17743,7 @@
     </row>
     <row r="163" ht="15.0" customHeight="1">
       <c r="A163" s="14" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B163" s="15"/>
       <c r="C163" s="21">
@@ -17804,7 +17810,7 @@
     </row>
     <row r="164" ht="15.0" customHeight="1">
       <c r="A164" s="14" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B164" s="15"/>
       <c r="C164" s="15"/>
@@ -17837,7 +17843,7 @@
     </row>
     <row r="165" ht="15.0" customHeight="1">
       <c r="A165" s="14" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B165" s="15"/>
       <c r="C165" s="18">
@@ -17906,7 +17912,7 @@
     </row>
     <row r="166" ht="15.0" customHeight="1">
       <c r="A166" s="14" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B166" s="18">
         <v>5471.71</v>
@@ -17935,7 +17941,7 @@
     </row>
     <row r="167" ht="15.0" customHeight="1">
       <c r="A167" s="16" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B167" s="20">
         <v>5471.71</v>
@@ -18006,7 +18012,7 @@
     </row>
     <row r="168" ht="15.0" customHeight="1">
       <c r="A168" s="16" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B168" s="20">
         <v>5471.71</v>
@@ -18077,7 +18083,7 @@
     </row>
     <row r="169" ht="15.0" customHeight="1">
       <c r="A169" s="16" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B169" s="17">
         <v>22119.74</v>
@@ -18148,7 +18154,7 @@
     </row>
     <row r="170" ht="15.0" customHeight="1">
       <c r="A170" s="14" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B170" s="19">
         <v>96.3</v>
@@ -18219,7 +18225,7 @@
     </row>
     <row r="171" ht="15.0" customHeight="1">
       <c r="A171" s="14" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B171" s="19">
         <v>92.11</v>
@@ -18290,7 +18296,7 @@
     </row>
     <row r="172" ht="15.0" customHeight="1">
       <c r="A172" s="14" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B172" s="19">
         <v>4.19</v>
@@ -18361,7 +18367,7 @@
     </row>
     <row r="173" ht="15.0" customHeight="1">
       <c r="A173" s="14" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B173" s="15"/>
       <c r="C173" s="15"/>
@@ -18390,7 +18396,7 @@
     </row>
     <row r="174" ht="15.0" customHeight="1">
       <c r="A174" s="14" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B174" s="15"/>
       <c r="C174" s="15"/>
@@ -18427,7 +18433,7 @@
     </row>
     <row r="175" ht="15.0" customHeight="1">
       <c r="A175" s="14" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B175" s="15"/>
       <c r="C175" s="15"/>
@@ -18456,7 +18462,7 @@
     </row>
     <row r="176" ht="15.0" customHeight="1">
       <c r="A176" s="14" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B176" s="15"/>
       <c r="C176" s="15"/>
@@ -18485,7 +18491,7 @@
     </row>
     <row r="177" ht="15.0" customHeight="1">
       <c r="A177" s="14" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B177" s="15"/>
       <c r="C177" s="18">
@@ -18520,7 +18526,7 @@
     </row>
     <row r="178" ht="15.0" customHeight="1">
       <c r="A178" s="14" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B178" s="15"/>
       <c r="C178" s="18">
@@ -18579,7 +18585,7 @@
     </row>
     <row r="179" ht="15.0" customHeight="1">
       <c r="A179" s="14" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B179" s="15"/>
       <c r="C179" s="18">
@@ -18638,7 +18644,7 @@
     </row>
     <row r="180" ht="15.0" customHeight="1">
       <c r="A180" s="14" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B180" s="15"/>
       <c r="C180" s="19">
@@ -18689,7 +18695,7 @@
     </row>
     <row r="181" ht="15.0" customHeight="1">
       <c r="A181" s="14" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B181" s="15"/>
       <c r="C181" s="15"/>
@@ -18720,7 +18726,7 @@
     </row>
     <row r="182" ht="15.0" customHeight="1">
       <c r="A182" s="14" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B182" s="15"/>
       <c r="C182" s="15"/>
@@ -18761,7 +18767,7 @@
     </row>
     <row r="183" ht="15.0" customHeight="1">
       <c r="A183" s="14" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B183" s="15"/>
       <c r="C183" s="18">
@@ -18822,7 +18828,7 @@
     </row>
     <row r="184" ht="15.0" customHeight="1">
       <c r="A184" s="14" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B184" s="15"/>
       <c r="C184" s="15"/>
@@ -18855,7 +18861,7 @@
     </row>
     <row r="185" ht="15.0" customHeight="1">
       <c r="A185" s="14" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B185" s="15"/>
       <c r="C185" s="18">
@@ -18916,7 +18922,7 @@
     </row>
     <row r="186" ht="15.0" customHeight="1">
       <c r="A186" s="14" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B186" s="15"/>
       <c r="C186" s="18">
@@ -18977,7 +18983,7 @@
     </row>
     <row r="187" ht="15.0" customHeight="1">
       <c r="A187" s="14" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B187" s="15"/>
       <c r="C187" s="18">
@@ -19016,7 +19022,7 @@
     </row>
     <row r="188" ht="15.0" customHeight="1">
       <c r="A188" s="14" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B188" s="19">
         <v>96.3</v>
@@ -19087,7 +19093,7 @@
     </row>
     <row r="189" ht="15.0" customHeight="1">
       <c r="A189" s="14" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B189" s="19">
         <v>92.11</v>
@@ -19158,7 +19164,7 @@
     </row>
     <row r="190" ht="15.0" customHeight="1">
       <c r="A190" s="14" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B190" s="19">
         <v>4.19</v>
@@ -19229,7 +19235,7 @@
     </row>
     <row r="191" ht="15.0" customHeight="1">
       <c r="A191" s="14" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B191" s="19">
         <v>1.0</v>
@@ -20127,7 +20133,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -20513,70 +20519,70 @@
         <v>44</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q15" s="10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="R15" s="10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="S15" s="10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="T15" s="10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="U15" s="10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="V15" s="10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="W15" s="10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1" outlineLevel="1">
@@ -20652,7 +20658,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -20750,7 +20756,7 @@
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="14" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B20" s="15"/>
       <c r="C20" s="15"/>
@@ -20785,7 +20791,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="14" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B21" s="15"/>
       <c r="C21" s="15"/>
@@ -20818,7 +20824,7 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="14" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B22" s="15"/>
       <c r="C22" s="18">
@@ -20938,7 +20944,7 @@
     </row>
     <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="14" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B24" s="18">
         <v>1639.58</v>
@@ -21009,7 +21015,7 @@
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="14" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B25" s="15"/>
       <c r="C25" s="15"/>
@@ -21050,7 +21056,7 @@
     </row>
     <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="14" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B26" s="15"/>
       <c r="C26" s="15"/>
@@ -21091,7 +21097,7 @@
     </row>
     <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="14" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B27" s="22">
         <v>-254.2</v>
@@ -21162,7 +21168,7 @@
     </row>
     <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="14" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B28" s="15"/>
       <c r="C28" s="15"/>
@@ -21207,7 +21213,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="14" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B29" s="15"/>
       <c r="C29" s="15"/>
@@ -21248,7 +21254,7 @@
     </row>
     <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="14" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B30" s="15"/>
       <c r="C30" s="15"/>
@@ -21293,7 +21299,7 @@
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="14" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B31" s="15"/>
       <c r="C31" s="15"/>
@@ -21336,7 +21342,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="14" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B32" s="15"/>
       <c r="C32" s="15"/>
@@ -21367,7 +21373,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="14" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B33" s="15"/>
       <c r="C33" s="15"/>
@@ -21412,7 +21418,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B34" s="15"/>
       <c r="C34" s="15"/>
@@ -21443,7 +21449,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="14" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B35" s="22">
         <v>-228.78</v>
@@ -21514,7 +21520,7 @@
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="14" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B36" s="18">
         <v>195.95</v>
@@ -21585,7 +21591,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="14" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B37" s="19">
         <v>85.79</v>
@@ -21656,7 +21662,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="14" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B38" s="19">
         <v>74.14</v>
@@ -21727,7 +21733,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="14" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B39" s="15"/>
       <c r="C39" s="15"/>
@@ -21760,7 +21766,7 @@
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="14" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B40" s="15"/>
       <c r="C40" s="15"/>
@@ -21793,7 +21799,7 @@
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="14" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B41" s="15"/>
       <c r="C41" s="15"/>
@@ -21826,7 +21832,7 @@
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="14" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B42" s="15"/>
       <c r="C42" s="15"/>
@@ -21859,7 +21865,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="14" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B43" s="15"/>
       <c r="C43" s="15"/>
@@ -21892,7 +21898,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="14" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B44" s="15"/>
       <c r="C44" s="21">
@@ -21921,7 +21927,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="16" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B45" s="20">
         <v>2490.09</v>
@@ -21992,7 +21998,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="14" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B46" s="22">
         <v>-420.49</v>
@@ -22061,7 +22067,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="14" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B47" s="18">
         <v>334.7</v>
@@ -22124,7 +22130,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="14" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B48" s="15"/>
       <c r="C48" s="15"/>
@@ -22155,7 +22161,7 @@
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="14" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B49" s="22">
         <v>-1434.11</v>
@@ -22210,7 +22216,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B50" s="18">
         <v>1262.52</v>
@@ -22271,7 +22277,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="14" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B51" s="15"/>
       <c r="C51" s="22">
@@ -22328,7 +22334,7 @@
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="14" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B52" s="18">
         <v>121.8</v>
@@ -22357,7 +22363,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="14" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B53" s="22">
         <v>-401.42</v>
@@ -22426,7 +22432,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="14" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B54" s="15"/>
       <c r="C54" s="15">
@@ -22483,7 +22489,7 @@
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="14" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B55" s="18">
         <v>259.49</v>
@@ -22538,7 +22544,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="14" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B56" s="15"/>
       <c r="C56" s="15"/>
@@ -22569,7 +22575,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="14" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B57" s="15"/>
       <c r="C57" s="15"/>
@@ -22612,7 +22618,7 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="14" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B58" s="19">
         <v>1.06</v>
@@ -22643,7 +22649,7 @@
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="16" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B59" s="25">
         <v>-276.44</v>
@@ -22714,7 +22720,7 @@
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="14" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B60" s="18">
         <v>864.28</v>
@@ -22771,7 +22777,7 @@
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="14" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B61" s="22">
         <v>-541.23</v>
@@ -22828,7 +22834,7 @@
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="14" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B62" s="22">
         <v>-983.96</v>
@@ -22885,7 +22891,7 @@
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="14" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B63" s="15"/>
       <c r="C63" s="15"/>
@@ -22930,7 +22936,7 @@
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="14" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B64" s="15"/>
       <c r="C64" s="15"/>
@@ -22961,7 +22967,7 @@
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="14" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B65" s="22">
         <v>-818.73</v>
@@ -23008,7 +23014,7 @@
     </row>
     <row r="66" ht="15.0" customHeight="1">
       <c r="A66" s="14" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B66" s="15"/>
       <c r="C66" s="15"/>
@@ -23039,7 +23045,7 @@
     </row>
     <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="14" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B67" s="15"/>
       <c r="C67" s="15"/>
@@ -23072,7 +23078,7 @@
     </row>
     <row r="68" ht="15.0" customHeight="1">
       <c r="A68" s="14" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B68" s="21">
         <v>-60.37</v>
@@ -23127,7 +23133,7 @@
     </row>
     <row r="69" ht="15.0" customHeight="1">
       <c r="A69" s="14" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B69" s="22">
         <v>-573.01</v>
@@ -23198,7 +23204,7 @@
     </row>
     <row r="70" ht="15.0" customHeight="1">
       <c r="A70" s="14" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B70" s="15"/>
       <c r="C70" s="15"/>
@@ -23229,7 +23235,7 @@
     </row>
     <row r="71" ht="15.0" customHeight="1">
       <c r="A71" s="14" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B71" s="15"/>
       <c r="C71" s="15"/>
@@ -23260,7 +23266,7 @@
     </row>
     <row r="72" ht="15.0" customHeight="1">
       <c r="A72" s="14" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B72" s="15"/>
       <c r="C72" s="15"/>
@@ -23291,7 +23297,7 @@
     </row>
     <row r="73" ht="15.0" customHeight="1">
       <c r="A73" s="14" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B73" s="21">
         <v>-1.06</v>
@@ -23320,7 +23326,7 @@
     </row>
     <row r="74" ht="15.0" customHeight="1">
       <c r="A74" s="16" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B74" s="25">
         <v>-2114.09</v>
@@ -23391,7 +23397,7 @@
     </row>
     <row r="75" ht="15.0" customHeight="1">
       <c r="A75" s="14" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B75" s="19">
         <v>14.83</v>
@@ -23462,7 +23468,7 @@
     </row>
     <row r="76" ht="15.0" customHeight="1">
       <c r="A76" s="14" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B76" s="19">
         <v>99.56</v>
@@ -23517,7 +23523,7 @@
     </row>
     <row r="77" ht="15.0" customHeight="1">
       <c r="A77" s="14" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B77" s="21">
         <v>-1.06</v>
@@ -23552,7 +23558,7 @@
     </row>
     <row r="78" ht="15.0" customHeight="1">
       <c r="A78" s="14" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B78" s="18">
         <v>478.94</v>
@@ -23623,7 +23629,7 @@
     </row>
     <row r="79" ht="15.0" customHeight="1">
       <c r="A79" s="14" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B79" s="18">
         <v>361.94</v>
@@ -23694,7 +23700,7 @@
     </row>
     <row r="80" ht="15.0" customHeight="1">
       <c r="A80" s="16" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B80" s="20">
         <v>113.33</v>
@@ -23765,7 +23771,7 @@
     </row>
     <row r="81" ht="15.0" customHeight="1">
       <c r="A81" s="14" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B81" s="15"/>
       <c r="C81" s="15"/>
@@ -23802,7 +23808,7 @@
     </row>
     <row r="82" ht="15.0" customHeight="1">
       <c r="A82" s="14" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B82" s="15"/>
       <c r="C82" s="15"/>
@@ -23839,7 +23845,7 @@
     </row>
     <row r="83" ht="15.0" customHeight="1">
       <c r="A83" s="14" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B83" s="15"/>
       <c r="C83" s="15"/>
@@ -23876,7 +23882,7 @@
     </row>
     <row r="84" ht="15.0" customHeight="1">
       <c r="A84" s="14" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B84" s="15"/>
       <c r="C84" s="15"/>
@@ -23905,7 +23911,7 @@
     </row>
     <row r="85" ht="15.0" customHeight="1">
       <c r="A85" s="14" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B85" s="15"/>
       <c r="C85" s="15"/>
@@ -24872,7 +24878,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -25043,25 +25049,25 @@
         <v>39</v>
       </c>
       <c r="W11" s="7" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="X11" s="7" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="Y11" s="7" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="Z11" s="7" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AA11" s="7" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AB11" s="7" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AC11" s="7" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="12" ht="15.0" customHeight="1" outlineLevel="1">
@@ -25511,7 +25517,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -25610,3495 +25616,3495 @@
         <v>71</v>
       </c>
       <c r="W19" s="13" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="X19" s="13" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="Y19" s="13" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="Z19" s="13" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AA19" s="13" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AB19" s="13" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AC19" s="13" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="1">
-      <c r="A20" s="26" t="s">
-        <v>439</v>
-      </c>
-      <c r="B20" s="27"/>
-      <c r="C20" s="27"/>
-      <c r="D20" s="27"/>
-      <c r="E20" s="27"/>
-      <c r="F20" s="27"/>
-      <c r="G20" s="27"/>
-      <c r="H20" s="27"/>
-      <c r="I20" s="27"/>
-      <c r="J20" s="27"/>
-      <c r="K20" s="27"/>
-      <c r="L20" s="27"/>
-      <c r="M20" s="27"/>
-      <c r="N20" s="27"/>
-      <c r="O20" s="27"/>
-      <c r="P20" s="27"/>
-      <c r="Q20" s="27"/>
-      <c r="R20" s="27"/>
-      <c r="S20" s="27"/>
-      <c r="T20" s="27"/>
-      <c r="U20" s="27"/>
-      <c r="V20" s="27"/>
-      <c r="W20" s="27"/>
-      <c r="X20" s="27"/>
-      <c r="Y20" s="27"/>
-      <c r="Z20" s="27"/>
-      <c r="AA20" s="27"/>
-      <c r="AB20" s="27"/>
-      <c r="AC20" s="27"/>
+      <c r="A20" s="27" t="s">
+        <v>440</v>
+      </c>
+      <c r="B20" s="28"/>
+      <c r="C20" s="28"/>
+      <c r="D20" s="28"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="28"/>
+      <c r="H20" s="28"/>
+      <c r="I20" s="28"/>
+      <c r="J20" s="28"/>
+      <c r="K20" s="28"/>
+      <c r="L20" s="28"/>
+      <c r="M20" s="28"/>
+      <c r="N20" s="28"/>
+      <c r="O20" s="28"/>
+      <c r="P20" s="28"/>
+      <c r="Q20" s="28"/>
+      <c r="R20" s="28"/>
+      <c r="S20" s="28"/>
+      <c r="T20" s="28"/>
+      <c r="U20" s="28"/>
+      <c r="V20" s="28"/>
+      <c r="W20" s="28"/>
+      <c r="X20" s="28"/>
+      <c r="Y20" s="28"/>
+      <c r="Z20" s="28"/>
+      <c r="AA20" s="28"/>
+      <c r="AB20" s="28"/>
+      <c r="AC20" s="28"/>
     </row>
     <row r="21" ht="15.0" customHeight="1">
-      <c r="A21" s="28" t="s">
-        <v>439</v>
-      </c>
-      <c r="B21" s="29">
+      <c r="A21" s="29" t="s">
+        <v>440</v>
+      </c>
+      <c r="B21" s="30">
         <v>23047.24</v>
       </c>
-      <c r="C21" s="29">
+      <c r="C21" s="30">
         <v>22664.26</v>
       </c>
-      <c r="D21" s="29">
+      <c r="D21" s="30">
         <v>17073.69</v>
       </c>
-      <c r="E21" s="29">
+      <c r="E21" s="30">
         <v>21707.47</v>
       </c>
-      <c r="F21" s="29">
+      <c r="F21" s="30">
         <v>16430.41</v>
       </c>
-      <c r="G21" s="29">
+      <c r="G21" s="30">
         <v>17539.58</v>
       </c>
-      <c r="H21" s="29">
+      <c r="H21" s="30">
         <v>12936.95</v>
       </c>
-      <c r="I21" s="29">
+      <c r="I21" s="30">
         <v>12684.19</v>
       </c>
-      <c r="J21" s="29">
+      <c r="J21" s="30">
         <v>13689.26</v>
       </c>
-      <c r="K21" s="29">
+      <c r="K21" s="30">
         <v>11560.05</v>
       </c>
-      <c r="L21" s="30">
+      <c r="L21" s="31">
         <v>5918.23</v>
       </c>
-      <c r="M21" s="30">
+      <c r="M21" s="31">
         <v>4567.98</v>
       </c>
-      <c r="N21" s="30">
+      <c r="N21" s="31">
         <v>2661.42</v>
       </c>
-      <c r="O21" s="30">
+      <c r="O21" s="31">
         <v>2338.03</v>
       </c>
-      <c r="P21" s="30">
+      <c r="P21" s="31">
         <v>2986.88</v>
       </c>
-      <c r="Q21" s="30">
+      <c r="Q21" s="31">
         <v>1464.49</v>
       </c>
-      <c r="R21" s="30">
+      <c r="R21" s="31">
         <v>969.7</v>
       </c>
-      <c r="S21" s="30">
+      <c r="S21" s="31">
         <v>2909.5</v>
       </c>
-      <c r="T21" s="30">
+      <c r="T21" s="31">
         <v>2432.0</v>
       </c>
-      <c r="U21" s="30">
+      <c r="U21" s="31">
         <v>3098.51</v>
       </c>
-      <c r="V21" s="30">
+      <c r="V21" s="31">
         <v>2168.79</v>
       </c>
-      <c r="W21" s="30">
+      <c r="W21" s="31">
         <v>3184.18</v>
       </c>
-      <c r="X21" s="30">
+      <c r="X21" s="31">
         <v>3339.84</v>
       </c>
-      <c r="Y21" s="30">
+      <c r="Y21" s="31">
         <v>2997.74</v>
       </c>
-      <c r="Z21" s="30">
+      <c r="Z21" s="31">
         <v>4025.73</v>
       </c>
-      <c r="AA21" s="30">
+      <c r="AA21" s="31">
         <v>4264.24</v>
       </c>
-      <c r="AB21" s="30">
+      <c r="AB21" s="31">
         <v>3747.19</v>
       </c>
-      <c r="AC21" s="30">
+      <c r="AC21" s="31">
         <v>4698.92</v>
       </c>
     </row>
     <row r="22" ht="15.0" customHeight="1">
-      <c r="A22" s="28" t="s">
-        <v>440</v>
-      </c>
-      <c r="B22" s="29">
+      <c r="A22" s="29" t="s">
+        <v>441</v>
+      </c>
+      <c r="B22" s="30">
         <v>20784.79</v>
       </c>
-      <c r="C22" s="29">
+      <c r="C22" s="30">
         <v>19606.17</v>
       </c>
-      <c r="D22" s="29">
+      <c r="D22" s="30">
         <v>16588.32</v>
       </c>
-      <c r="E22" s="29">
+      <c r="E22" s="30">
         <v>16105.62</v>
       </c>
-      <c r="F22" s="29">
+      <c r="F22" s="30">
         <v>15623.08</v>
       </c>
-      <c r="G22" s="29">
+      <c r="G22" s="30">
         <v>13149.71</v>
       </c>
-      <c r="H22" s="29">
+      <c r="H22" s="30">
         <v>11239.65</v>
       </c>
-      <c r="I22" s="30">
+      <c r="I22" s="31">
         <v>9842.03</v>
       </c>
-      <c r="J22" s="30">
+      <c r="J22" s="31">
         <v>7512.84</v>
       </c>
-      <c r="K22" s="30">
+      <c r="K22" s="31">
         <v>5833.67</v>
       </c>
-      <c r="L22" s="30">
+      <c r="L22" s="31">
         <v>3885.26</v>
       </c>
-      <c r="M22" s="30">
+      <c r="M22" s="31">
         <v>2997.55</v>
       </c>
-      <c r="N22" s="30">
+      <c r="N22" s="31">
         <v>2079.55</v>
       </c>
-      <c r="O22" s="30">
+      <c r="O22" s="31">
         <v>2168.76</v>
       </c>
-      <c r="P22" s="30">
+      <c r="P22" s="31">
         <v>2164.55</v>
       </c>
-      <c r="Q22" s="30">
+      <c r="Q22" s="31">
         <v>2051.9</v>
       </c>
-      <c r="R22" s="30">
+      <c r="R22" s="31">
         <v>2355.46</v>
       </c>
-      <c r="S22" s="30">
+      <c r="S22" s="31">
         <v>2622.0</v>
       </c>
-      <c r="T22" s="30">
+      <c r="T22" s="31">
         <v>2970.83</v>
       </c>
-      <c r="U22" s="30">
+      <c r="U22" s="31">
         <v>2911.61</v>
       </c>
-      <c r="V22" s="30">
+      <c r="V22" s="31">
         <v>3254.65</v>
       </c>
-      <c r="W22" s="30">
+      <c r="W22" s="31">
         <v>3702.4</v>
       </c>
-      <c r="X22" s="30">
+      <c r="X22" s="31">
         <v>3275.05</v>
       </c>
-      <c r="Y22" s="30">
+      <c r="Y22" s="31">
         <v>3662.53</v>
       </c>
-      <c r="Z22" s="29"/>
-      <c r="AA22" s="29"/>
-      <c r="AB22" s="29"/>
-      <c r="AC22" s="29"/>
+      <c r="Z22" s="30"/>
+      <c r="AA22" s="30"/>
+      <c r="AB22" s="30"/>
+      <c r="AC22" s="30"/>
     </row>
     <row r="23" ht="15.0" customHeight="1">
-      <c r="A23" s="26" t="s">
-        <v>441</v>
-      </c>
-      <c r="B23" s="27"/>
-      <c r="C23" s="27"/>
-      <c r="D23" s="27"/>
-      <c r="E23" s="27"/>
-      <c r="F23" s="27"/>
-      <c r="G23" s="27"/>
-      <c r="H23" s="27"/>
-      <c r="I23" s="27"/>
-      <c r="J23" s="27"/>
-      <c r="K23" s="27"/>
-      <c r="L23" s="27"/>
-      <c r="M23" s="27"/>
-      <c r="N23" s="27"/>
-      <c r="O23" s="27"/>
-      <c r="P23" s="27"/>
-      <c r="Q23" s="27"/>
-      <c r="R23" s="27"/>
-      <c r="S23" s="27"/>
-      <c r="T23" s="27"/>
-      <c r="U23" s="27"/>
-      <c r="V23" s="27"/>
-      <c r="W23" s="27"/>
-      <c r="X23" s="27"/>
-      <c r="Y23" s="27"/>
-      <c r="Z23" s="27"/>
-      <c r="AA23" s="27"/>
-      <c r="AB23" s="27"/>
-      <c r="AC23" s="27"/>
+      <c r="A23" s="27" t="s">
+        <v>442</v>
+      </c>
+      <c r="B23" s="28"/>
+      <c r="C23" s="28"/>
+      <c r="D23" s="28"/>
+      <c r="E23" s="28"/>
+      <c r="F23" s="28"/>
+      <c r="G23" s="28"/>
+      <c r="H23" s="28"/>
+      <c r="I23" s="28"/>
+      <c r="J23" s="28"/>
+      <c r="K23" s="28"/>
+      <c r="L23" s="28"/>
+      <c r="M23" s="28"/>
+      <c r="N23" s="28"/>
+      <c r="O23" s="28"/>
+      <c r="P23" s="28"/>
+      <c r="Q23" s="28"/>
+      <c r="R23" s="28"/>
+      <c r="S23" s="28"/>
+      <c r="T23" s="28"/>
+      <c r="U23" s="28"/>
+      <c r="V23" s="28"/>
+      <c r="W23" s="28"/>
+      <c r="X23" s="28"/>
+      <c r="Y23" s="28"/>
+      <c r="Z23" s="28"/>
+      <c r="AA23" s="28"/>
+      <c r="AB23" s="28"/>
+      <c r="AC23" s="28"/>
     </row>
     <row r="24" ht="15.0" customHeight="1">
-      <c r="A24" s="28" t="s">
-        <v>441</v>
-      </c>
-      <c r="B24" s="29">
+      <c r="A24" s="29" t="s">
+        <v>442</v>
+      </c>
+      <c r="B24" s="30">
         <v>11949.97</v>
       </c>
-      <c r="C24" s="29">
+      <c r="C24" s="30">
         <v>13049.66</v>
       </c>
-      <c r="D24" s="29">
+      <c r="D24" s="30">
         <v>10360.59</v>
       </c>
-      <c r="E24" s="29">
+      <c r="E24" s="30">
         <v>16044.96</v>
       </c>
-      <c r="F24" s="29">
+      <c r="F24" s="30">
         <v>10884.66</v>
       </c>
-      <c r="G24" s="29">
+      <c r="G24" s="30">
         <v>10246.44</v>
       </c>
-      <c r="H24" s="30">
+      <c r="H24" s="31">
         <v>8311.37</v>
       </c>
-      <c r="I24" s="30">
+      <c r="I24" s="31">
         <v>8229.31</v>
       </c>
-      <c r="J24" s="29">
+      <c r="J24" s="30">
         <v>10211.77</v>
       </c>
-      <c r="K24" s="29">
+      <c r="K24" s="30">
         <v>10134.63</v>
       </c>
-      <c r="L24" s="30">
+      <c r="L24" s="31">
         <v>5729.41</v>
       </c>
-      <c r="M24" s="30">
+      <c r="M24" s="31">
         <v>3885.64</v>
       </c>
-      <c r="N24" s="30">
+      <c r="N24" s="31">
         <v>2009.98</v>
       </c>
-      <c r="O24" s="30">
+      <c r="O24" s="31">
         <v>2105.49</v>
       </c>
-      <c r="P24" s="30">
+      <c r="P24" s="31">
         <v>2796.0</v>
       </c>
-      <c r="Q24" s="30">
+      <c r="Q24" s="31">
         <v>1350.41</v>
       </c>
-      <c r="R24" s="30">
+      <c r="R24" s="31">
         <v>307.22</v>
       </c>
-      <c r="S24" s="30">
+      <c r="S24" s="31">
         <v>1849.84</v>
       </c>
-      <c r="T24" s="30">
+      <c r="T24" s="31">
         <v>2321.82</v>
       </c>
-      <c r="U24" s="30">
+      <c r="U24" s="31">
         <v>2316.44</v>
       </c>
-      <c r="V24" s="30">
+      <c r="V24" s="31">
         <v>2055.53</v>
       </c>
-      <c r="W24" s="30">
+      <c r="W24" s="31">
         <v>2752.16</v>
       </c>
-      <c r="X24" s="30">
+      <c r="X24" s="31">
         <v>1564.12</v>
       </c>
-      <c r="Y24" s="30">
+      <c r="Y24" s="31">
         <v>1398.36</v>
       </c>
-      <c r="Z24" s="30">
+      <c r="Z24" s="31">
         <v>1513.18</v>
       </c>
-      <c r="AA24" s="30">
+      <c r="AA24" s="31">
         <v>1765.7</v>
       </c>
-      <c r="AB24" s="30">
+      <c r="AB24" s="31">
         <v>1304.16</v>
       </c>
-      <c r="AC24" s="30">
+      <c r="AC24" s="31">
         <v>2555.27</v>
       </c>
     </row>
     <row r="25" ht="15.0" customHeight="1">
-      <c r="A25" s="28" t="s">
-        <v>442</v>
-      </c>
-      <c r="B25" s="29">
+      <c r="A25" s="29" t="s">
+        <v>443</v>
+      </c>
+      <c r="B25" s="30">
         <v>12848.1</v>
       </c>
-      <c r="C25" s="29">
+      <c r="C25" s="30">
         <v>12441.43</v>
       </c>
-      <c r="D25" s="29">
+      <c r="D25" s="30">
         <v>10795.21</v>
       </c>
-      <c r="E25" s="29">
+      <c r="E25" s="30">
         <v>10631.54</v>
       </c>
-      <c r="F25" s="29">
+      <c r="F25" s="30">
         <v>10204.1</v>
       </c>
-      <c r="G25" s="30">
+      <c r="G25" s="31">
         <v>9024.18</v>
       </c>
-      <c r="H25" s="30">
+      <c r="H25" s="31">
         <v>8425.66</v>
       </c>
-      <c r="I25" s="30">
+      <c r="I25" s="31">
         <v>7760.29</v>
       </c>
-      <c r="J25" s="30">
+      <c r="J25" s="31">
         <v>6240.01</v>
       </c>
-      <c r="K25" s="30">
+      <c r="K25" s="31">
         <v>5140.43</v>
       </c>
-      <c r="L25" s="30">
+      <c r="L25" s="31">
         <v>3469.27</v>
       </c>
-      <c r="M25" s="30">
+      <c r="M25" s="31">
         <v>2599.08</v>
       </c>
-      <c r="N25" s="30">
+      <c r="N25" s="31">
         <v>1714.03</v>
       </c>
-      <c r="O25" s="30">
+      <c r="O25" s="31">
         <v>1711.65</v>
       </c>
-      <c r="P25" s="30">
+      <c r="P25" s="31">
         <v>1732.97</v>
       </c>
-      <c r="Q25" s="30">
+      <c r="Q25" s="31">
         <v>1536.01</v>
       </c>
-      <c r="R25" s="30">
+      <c r="R25" s="31">
         <v>1791.51</v>
       </c>
-      <c r="S25" s="30">
+      <c r="S25" s="31">
         <v>2135.56</v>
       </c>
-      <c r="T25" s="30">
+      <c r="T25" s="31">
         <v>2268.45</v>
       </c>
-      <c r="U25" s="30">
+      <c r="U25" s="31">
         <v>1959.88</v>
       </c>
-      <c r="V25" s="30">
+      <c r="V25" s="31">
         <v>1906.49</v>
       </c>
-      <c r="W25" s="30">
+      <c r="W25" s="31">
         <v>1865.31</v>
       </c>
-      <c r="X25" s="30">
+      <c r="X25" s="31">
         <v>1353.28</v>
       </c>
-      <c r="Y25" s="30">
+      <c r="Y25" s="31">
         <v>1586.93</v>
       </c>
-      <c r="Z25" s="29"/>
-      <c r="AA25" s="29"/>
-      <c r="AB25" s="29"/>
-      <c r="AC25" s="29"/>
+      <c r="Z25" s="30"/>
+      <c r="AA25" s="30"/>
+      <c r="AB25" s="30"/>
+      <c r="AC25" s="30"/>
     </row>
     <row r="26" ht="15.0" customHeight="1">
-      <c r="A26" s="26" t="s">
-        <v>443</v>
-      </c>
-      <c r="B26" s="27"/>
-      <c r="C26" s="27"/>
-      <c r="D26" s="27"/>
-      <c r="E26" s="27"/>
-      <c r="F26" s="27"/>
-      <c r="G26" s="27"/>
-      <c r="H26" s="27"/>
-      <c r="I26" s="27"/>
-      <c r="J26" s="27"/>
-      <c r="K26" s="27"/>
-      <c r="L26" s="27"/>
-      <c r="M26" s="27"/>
-      <c r="N26" s="27"/>
-      <c r="O26" s="27"/>
-      <c r="P26" s="27"/>
-      <c r="Q26" s="27"/>
-      <c r="R26" s="27"/>
-      <c r="S26" s="27"/>
-      <c r="T26" s="27"/>
-      <c r="U26" s="27"/>
-      <c r="V26" s="27"/>
-      <c r="W26" s="27"/>
-      <c r="X26" s="27"/>
-      <c r="Y26" s="27"/>
-      <c r="Z26" s="27"/>
-      <c r="AA26" s="27"/>
-      <c r="AB26" s="27"/>
-      <c r="AC26" s="27"/>
+      <c r="A26" s="27" t="s">
+        <v>444</v>
+      </c>
+      <c r="B26" s="28"/>
+      <c r="C26" s="28"/>
+      <c r="D26" s="28"/>
+      <c r="E26" s="28"/>
+      <c r="F26" s="28"/>
+      <c r="G26" s="28"/>
+      <c r="H26" s="28"/>
+      <c r="I26" s="28"/>
+      <c r="J26" s="28"/>
+      <c r="K26" s="28"/>
+      <c r="L26" s="28"/>
+      <c r="M26" s="28"/>
+      <c r="N26" s="28"/>
+      <c r="O26" s="28"/>
+      <c r="P26" s="28"/>
+      <c r="Q26" s="28"/>
+      <c r="R26" s="28"/>
+      <c r="S26" s="28"/>
+      <c r="T26" s="28"/>
+      <c r="U26" s="28"/>
+      <c r="V26" s="28"/>
+      <c r="W26" s="28"/>
+      <c r="X26" s="28"/>
+      <c r="Y26" s="28"/>
+      <c r="Z26" s="28"/>
+      <c r="AA26" s="28"/>
+      <c r="AB26" s="28"/>
+      <c r="AC26" s="28"/>
     </row>
     <row r="27" ht="15.0" customHeight="1">
-      <c r="A27" s="28" t="s">
-        <v>444</v>
-      </c>
-      <c r="B27" s="30">
+      <c r="A27" s="29" t="s">
+        <v>445</v>
+      </c>
+      <c r="B27" s="31">
         <v>124.09</v>
       </c>
-      <c r="C27" s="30">
+      <c r="C27" s="31">
         <v>135.51</v>
       </c>
-      <c r="D27" s="30">
+      <c r="D27" s="31">
         <v>107.59</v>
       </c>
-      <c r="E27" s="29"/>
-      <c r="F27" s="30">
+      <c r="E27" s="30"/>
+      <c r="F27" s="31">
         <v>105.88</v>
       </c>
-      <c r="G27" s="31">
+      <c r="G27" s="32">
         <v>99.67</v>
       </c>
-      <c r="H27" s="31">
+      <c r="H27" s="32">
         <v>80.85</v>
       </c>
-      <c r="I27" s="31">
+      <c r="I27" s="32">
         <v>80.05</v>
       </c>
-      <c r="J27" s="31">
+      <c r="J27" s="32">
         <v>99.34</v>
       </c>
-      <c r="K27" s="30">
+      <c r="K27" s="31">
         <v>100.47</v>
       </c>
-      <c r="L27" s="31">
+      <c r="L27" s="32">
         <v>56.91</v>
       </c>
-      <c r="M27" s="31">
+      <c r="M27" s="32">
         <v>38.64</v>
       </c>
-      <c r="N27" s="31">
+      <c r="N27" s="32">
         <v>20.01</v>
       </c>
-      <c r="O27" s="31">
+      <c r="O27" s="32">
         <v>20.99</v>
       </c>
-      <c r="P27" s="31">
+      <c r="P27" s="32">
         <v>28.09</v>
       </c>
-      <c r="Q27" s="31">
+      <c r="Q27" s="32">
         <v>14.11</v>
       </c>
-      <c r="R27" s="31">
+      <c r="R27" s="32">
         <v>3.58</v>
       </c>
-      <c r="S27" s="31">
+      <c r="S27" s="32">
         <v>21.55</v>
       </c>
-      <c r="T27" s="31">
+      <c r="T27" s="32">
         <v>25.1</v>
       </c>
-      <c r="U27" s="31">
+      <c r="U27" s="32">
         <v>25.04</v>
       </c>
-      <c r="V27" s="31">
+      <c r="V27" s="32">
         <v>20.0</v>
       </c>
-      <c r="W27" s="31">
+      <c r="W27" s="32">
         <v>16.82</v>
       </c>
-      <c r="X27" s="31">
+      <c r="X27" s="32">
         <v>8.6</v>
       </c>
-      <c r="Y27" s="31">
+      <c r="Y27" s="32">
         <v>7.69</v>
       </c>
-      <c r="Z27" s="31">
+      <c r="Z27" s="32">
         <v>7.5</v>
       </c>
-      <c r="AA27" s="31">
+      <c r="AA27" s="32">
         <v>8.76</v>
       </c>
-      <c r="AB27" s="31">
+      <c r="AB27" s="32">
         <v>6.47</v>
       </c>
-      <c r="AC27" s="31">
+      <c r="AC27" s="32">
         <v>12.67</v>
       </c>
     </row>
     <row r="28" ht="15.0" customHeight="1">
-      <c r="A28" s="28" t="s">
-        <v>445</v>
-      </c>
-      <c r="B28" s="30">
+      <c r="A28" s="29" t="s">
+        <v>446</v>
+      </c>
+      <c r="B28" s="31">
         <v>129.79</v>
       </c>
-      <c r="C28" s="30">
+      <c r="C28" s="31">
         <v>124.19</v>
       </c>
-      <c r="D28" s="30">
+      <c r="D28" s="31">
         <v>106.37</v>
       </c>
-      <c r="E28" s="29"/>
-      <c r="F28" s="31">
+      <c r="E28" s="30"/>
+      <c r="F28" s="32">
         <v>99.26</v>
       </c>
-      <c r="G28" s="31">
+      <c r="G28" s="32">
         <v>88.12</v>
       </c>
-      <c r="H28" s="31">
+      <c r="H28" s="32">
         <v>82.55</v>
       </c>
-      <c r="I28" s="31">
+      <c r="I28" s="32">
         <v>76.27</v>
       </c>
-      <c r="J28" s="31">
+      <c r="J28" s="32">
         <v>61.55</v>
       </c>
-      <c r="K28" s="31">
+      <c r="K28" s="32">
         <v>51.06</v>
       </c>
-      <c r="L28" s="31">
+      <c r="L28" s="32">
         <v>34.57</v>
       </c>
-      <c r="M28" s="31">
+      <c r="M28" s="32">
         <v>26.08</v>
       </c>
-      <c r="N28" s="31">
+      <c r="N28" s="32">
         <v>17.36</v>
       </c>
-      <c r="O28" s="31">
+      <c r="O28" s="32">
         <v>17.99</v>
       </c>
-      <c r="P28" s="31">
+      <c r="P28" s="32">
         <v>18.57</v>
       </c>
-      <c r="Q28" s="31">
+      <c r="Q28" s="32">
         <v>16.85</v>
       </c>
-      <c r="R28" s="31">
+      <c r="R28" s="32">
         <v>19.31</v>
       </c>
-      <c r="S28" s="31">
+      <c r="S28" s="32">
         <v>20.64</v>
       </c>
-      <c r="T28" s="31">
+      <c r="T28" s="32">
         <v>19.64</v>
       </c>
-      <c r="U28" s="31">
+      <c r="U28" s="32">
         <v>15.16</v>
       </c>
-      <c r="V28" s="31">
+      <c r="V28" s="32">
         <v>12.4</v>
       </c>
-      <c r="W28" s="31">
+      <c r="W28" s="32">
         <v>10.25</v>
       </c>
-      <c r="X28" s="31">
+      <c r="X28" s="32">
         <v>7.02</v>
       </c>
-      <c r="Y28" s="31">
+      <c r="Y28" s="32">
         <v>8.02</v>
       </c>
-      <c r="Z28" s="29"/>
-      <c r="AA28" s="29"/>
-      <c r="AB28" s="29"/>
-      <c r="AC28" s="29"/>
+      <c r="Z28" s="30"/>
+      <c r="AA28" s="30"/>
+      <c r="AB28" s="30"/>
+      <c r="AC28" s="30"/>
     </row>
     <row r="29" ht="15.0" customHeight="1">
-      <c r="A29" s="26" t="s">
-        <v>446</v>
-      </c>
-      <c r="B29" s="27"/>
-      <c r="C29" s="27"/>
-      <c r="D29" s="27"/>
-      <c r="E29" s="27"/>
-      <c r="F29" s="27"/>
-      <c r="G29" s="27"/>
-      <c r="H29" s="27"/>
-      <c r="I29" s="27"/>
-      <c r="J29" s="27"/>
-      <c r="K29" s="27"/>
-      <c r="L29" s="27"/>
-      <c r="M29" s="27"/>
-      <c r="N29" s="27"/>
-      <c r="O29" s="27"/>
-      <c r="P29" s="27"/>
-      <c r="Q29" s="27"/>
-      <c r="R29" s="27"/>
-      <c r="S29" s="27"/>
-      <c r="T29" s="27"/>
-      <c r="U29" s="27"/>
-      <c r="V29" s="27"/>
-      <c r="W29" s="27"/>
-      <c r="X29" s="27"/>
-      <c r="Y29" s="27"/>
-      <c r="Z29" s="27"/>
-      <c r="AA29" s="27"/>
-      <c r="AB29" s="27"/>
-      <c r="AC29" s="27"/>
+      <c r="A29" s="27" t="s">
+        <v>447</v>
+      </c>
+      <c r="B29" s="28"/>
+      <c r="C29" s="28"/>
+      <c r="D29" s="28"/>
+      <c r="E29" s="28"/>
+      <c r="F29" s="28"/>
+      <c r="G29" s="28"/>
+      <c r="H29" s="28"/>
+      <c r="I29" s="28"/>
+      <c r="J29" s="28"/>
+      <c r="K29" s="28"/>
+      <c r="L29" s="28"/>
+      <c r="M29" s="28"/>
+      <c r="N29" s="28"/>
+      <c r="O29" s="28"/>
+      <c r="P29" s="28"/>
+      <c r="Q29" s="28"/>
+      <c r="R29" s="28"/>
+      <c r="S29" s="28"/>
+      <c r="T29" s="28"/>
+      <c r="U29" s="28"/>
+      <c r="V29" s="28"/>
+      <c r="W29" s="28"/>
+      <c r="X29" s="28"/>
+      <c r="Y29" s="28"/>
+      <c r="Z29" s="28"/>
+      <c r="AA29" s="28"/>
+      <c r="AB29" s="28"/>
+      <c r="AC29" s="28"/>
     </row>
     <row r="30" ht="15.0" customHeight="1">
-      <c r="A30" s="28" t="s">
-        <v>447</v>
-      </c>
-      <c r="B30" s="32">
+      <c r="A30" s="29" t="s">
+        <v>448</v>
+      </c>
+      <c r="B30" s="33">
         <v>2.99</v>
       </c>
-      <c r="C30" s="33">
+      <c r="C30" s="34">
         <v>-4.01</v>
       </c>
-      <c r="D30" s="33">
+      <c r="D30" s="34">
         <v>-8.1</v>
       </c>
-      <c r="E30" s="32">
+      <c r="E30" s="33">
         <v>4.66</v>
       </c>
-      <c r="F30" s="32">
+      <c r="F30" s="33">
         <v>15.58</v>
       </c>
-      <c r="G30" s="33">
+      <c r="G30" s="34">
         <v>-4.37</v>
       </c>
-      <c r="H30" s="33">
+      <c r="H30" s="34">
         <v>-7.06</v>
       </c>
-      <c r="I30" s="33">
+      <c r="I30" s="34">
         <v>-7.52</v>
       </c>
-      <c r="J30" s="33">
+      <c r="J30" s="34">
         <v>-2.55</v>
       </c>
-      <c r="K30" s="33">
+      <c r="K30" s="34">
         <v>-3.52</v>
       </c>
-      <c r="L30" s="32">
+      <c r="L30" s="33">
         <v>1.09</v>
       </c>
-      <c r="M30" s="33">
+      <c r="M30" s="34">
         <v>-10.64</v>
       </c>
-      <c r="N30" s="32">
+      <c r="N30" s="33">
         <v>3.15</v>
       </c>
-      <c r="O30" s="32">
+      <c r="O30" s="33">
         <v>19.82</v>
       </c>
-      <c r="P30" s="33">
+      <c r="P30" s="34">
         <v>-4.67</v>
       </c>
-      <c r="Q30" s="32">
+      <c r="Q30" s="33">
         <v>29.53</v>
       </c>
-      <c r="R30" s="32">
+      <c r="R30" s="33">
         <v>101.4</v>
       </c>
-      <c r="S30" s="32"/>
-      <c r="T30" s="32">
+      <c r="S30" s="33"/>
+      <c r="T30" s="33">
         <v>6.91</v>
       </c>
-      <c r="U30" s="33">
+      <c r="U30" s="34">
         <v>-2.97</v>
       </c>
-      <c r="V30" s="33">
+      <c r="V30" s="34">
         <v>-1.42</v>
       </c>
-      <c r="W30" s="32">
+      <c r="W30" s="33">
         <v>6.38</v>
       </c>
-      <c r="X30" s="32">
+      <c r="X30" s="33">
         <v>15.13</v>
       </c>
-      <c r="Y30" s="32">
+      <c r="Y30" s="33">
         <v>64.93</v>
       </c>
-      <c r="Z30" s="33">
+      <c r="Z30" s="34">
         <v>-41.18</v>
       </c>
-      <c r="AA30" s="32">
+      <c r="AA30" s="33">
         <v>52.09</v>
       </c>
-      <c r="AB30" s="33">
+      <c r="AB30" s="34">
         <v>-36.08</v>
       </c>
-      <c r="AC30" s="32">
+      <c r="AC30" s="33">
         <v>15.58</v>
       </c>
     </row>
     <row r="31" ht="15.0" customHeight="1">
-      <c r="A31" s="28" t="s">
-        <v>448</v>
-      </c>
-      <c r="B31" s="32">
+      <c r="A31" s="29" t="s">
+        <v>449</v>
+      </c>
+      <c r="B31" s="33">
         <v>1.94</v>
       </c>
-      <c r="C31" s="32">
+      <c r="C31" s="33">
         <v>0.64</v>
       </c>
-      <c r="D31" s="32">
+      <c r="D31" s="33">
         <v>0.62</v>
       </c>
-      <c r="E31" s="32">
+      <c r="E31" s="33">
         <v>1.27</v>
       </c>
-      <c r="F31" s="33">
+      <c r="F31" s="34">
         <v>-0.71</v>
       </c>
-      <c r="G31" s="33">
+      <c r="G31" s="34">
         <v>-4.8</v>
       </c>
-      <c r="H31" s="33">
+      <c r="H31" s="34">
         <v>-4.08</v>
       </c>
-      <c r="I31" s="33">
+      <c r="I31" s="34">
         <v>-4.14</v>
       </c>
-      <c r="J31" s="33">
+      <c r="J31" s="34">
         <v>-2.78</v>
       </c>
-      <c r="K31" s="33">
+      <c r="K31" s="34">
         <v>-0.64</v>
       </c>
-      <c r="L31" s="32">
+      <c r="L31" s="33">
         <v>0.17</v>
       </c>
-      <c r="M31" s="32">
+      <c r="M31" s="33">
         <v>3.47</v>
       </c>
-      <c r="N31" s="32">
+      <c r="N31" s="33">
         <v>13.07</v>
       </c>
-      <c r="O31" s="32"/>
-      <c r="P31" s="32"/>
-      <c r="Q31" s="32"/>
-      <c r="R31" s="32"/>
-      <c r="S31" s="32"/>
-      <c r="T31" s="32">
+      <c r="O31" s="33"/>
+      <c r="P31" s="33"/>
+      <c r="Q31" s="33"/>
+      <c r="R31" s="33"/>
+      <c r="S31" s="33"/>
+      <c r="T31" s="33">
         <v>3.25</v>
       </c>
-      <c r="U31" s="32">
+      <c r="U31" s="33">
         <v>8.33</v>
       </c>
-      <c r="V31" s="32">
+      <c r="V31" s="33">
         <v>7.36</v>
       </c>
-      <c r="W31" s="32">
+      <c r="W31" s="33">
         <v>18.36</v>
       </c>
-      <c r="X31" s="32">
+      <c r="X31" s="33">
         <v>14.79</v>
       </c>
-      <c r="Y31" s="32">
+      <c r="Y31" s="33">
         <v>14.94</v>
       </c>
-      <c r="Z31" s="32"/>
-      <c r="AA31" s="32"/>
-      <c r="AB31" s="32"/>
-      <c r="AC31" s="32"/>
+      <c r="Z31" s="33"/>
+      <c r="AA31" s="33"/>
+      <c r="AB31" s="33"/>
+      <c r="AC31" s="33"/>
     </row>
     <row r="32" ht="15.0" customHeight="1">
-      <c r="A32" s="26" t="s">
-        <v>449</v>
-      </c>
-      <c r="B32" s="27"/>
-      <c r="C32" s="27"/>
-      <c r="D32" s="27"/>
-      <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
-      <c r="G32" s="27"/>
-      <c r="H32" s="27"/>
-      <c r="I32" s="27"/>
-      <c r="J32" s="27"/>
-      <c r="K32" s="27"/>
-      <c r="L32" s="27"/>
-      <c r="M32" s="27"/>
-      <c r="N32" s="27"/>
-      <c r="O32" s="27"/>
-      <c r="P32" s="27"/>
-      <c r="Q32" s="27"/>
-      <c r="R32" s="27"/>
-      <c r="S32" s="27"/>
-      <c r="T32" s="27"/>
-      <c r="U32" s="27"/>
-      <c r="V32" s="27"/>
-      <c r="W32" s="27"/>
-      <c r="X32" s="27"/>
-      <c r="Y32" s="27"/>
-      <c r="Z32" s="27"/>
-      <c r="AA32" s="27"/>
-      <c r="AB32" s="27"/>
-      <c r="AC32" s="27"/>
+      <c r="A32" s="27" t="s">
+        <v>450</v>
+      </c>
+      <c r="B32" s="28"/>
+      <c r="C32" s="28"/>
+      <c r="D32" s="28"/>
+      <c r="E32" s="28"/>
+      <c r="F32" s="28"/>
+      <c r="G32" s="28"/>
+      <c r="H32" s="28"/>
+      <c r="I32" s="28"/>
+      <c r="J32" s="28"/>
+      <c r="K32" s="28"/>
+      <c r="L32" s="28"/>
+      <c r="M32" s="28"/>
+      <c r="N32" s="28"/>
+      <c r="O32" s="28"/>
+      <c r="P32" s="28"/>
+      <c r="Q32" s="28"/>
+      <c r="R32" s="28"/>
+      <c r="S32" s="28"/>
+      <c r="T32" s="28"/>
+      <c r="U32" s="28"/>
+      <c r="V32" s="28"/>
+      <c r="W32" s="28"/>
+      <c r="X32" s="28"/>
+      <c r="Y32" s="28"/>
+      <c r="Z32" s="28"/>
+      <c r="AA32" s="28"/>
+      <c r="AB32" s="28"/>
+      <c r="AC32" s="28"/>
     </row>
     <row r="33" ht="15.0" customHeight="1">
-      <c r="A33" s="28" t="s">
-        <v>450</v>
-      </c>
-      <c r="B33" s="32">
+      <c r="A33" s="29" t="s">
+        <v>451</v>
+      </c>
+      <c r="B33" s="33">
         <v>3.83</v>
       </c>
-      <c r="C33" s="32">
+      <c r="C33" s="33">
         <v>4.58</v>
       </c>
-      <c r="D33" s="32">
+      <c r="D33" s="33">
         <v>4.9</v>
       </c>
-      <c r="E33" s="32"/>
-      <c r="F33" s="32">
+      <c r="E33" s="33"/>
+      <c r="F33" s="33">
         <v>0.0</v>
       </c>
-      <c r="G33" s="32">
+      <c r="G33" s="33">
         <v>3.13</v>
       </c>
-      <c r="H33" s="32">
+      <c r="H33" s="33">
         <v>3.8</v>
       </c>
-      <c r="I33" s="32">
+      <c r="I33" s="33">
         <v>3.5</v>
       </c>
-      <c r="J33" s="32">
+      <c r="J33" s="33">
         <v>2.51</v>
       </c>
-      <c r="K33" s="32">
+      <c r="K33" s="33">
         <v>2.19</v>
       </c>
-      <c r="L33" s="32">
+      <c r="L33" s="33">
         <v>2.65</v>
       </c>
-      <c r="M33" s="32">
+      <c r="M33" s="33">
         <v>2.56</v>
       </c>
-      <c r="N33" s="32">
+      <c r="N33" s="33">
         <v>7.11</v>
       </c>
-      <c r="O33" s="32">
+      <c r="O33" s="33">
         <v>8.68</v>
       </c>
-      <c r="P33" s="32">
+      <c r="P33" s="33">
         <v>1.62</v>
       </c>
-      <c r="Q33" s="32">
+      <c r="Q33" s="33">
         <v>0.0</v>
       </c>
-      <c r="R33" s="32">
+      <c r="R33" s="33">
         <v>34.78</v>
       </c>
-      <c r="S33" s="32">
+      <c r="S33" s="33">
         <v>5.46</v>
       </c>
-      <c r="T33" s="32">
+      <c r="T33" s="33">
         <v>5.08</v>
       </c>
-      <c r="U33" s="32">
+      <c r="U33" s="33">
         <v>6.36</v>
       </c>
-      <c r="V33" s="32">
+      <c r="V33" s="33">
         <v>5.14</v>
       </c>
-      <c r="W33" s="32">
+      <c r="W33" s="33">
         <v>3.68</v>
       </c>
-      <c r="X33" s="32">
+      <c r="X33" s="33">
         <v>5.83</v>
       </c>
-      <c r="Y33" s="32">
+      <c r="Y33" s="33">
         <v>6.56</v>
       </c>
-      <c r="Z33" s="32">
+      <c r="Z33" s="33">
         <v>6.83</v>
       </c>
-      <c r="AA33" s="32">
+      <c r="AA33" s="33">
         <v>5.07</v>
       </c>
-      <c r="AB33" s="32">
+      <c r="AB33" s="33">
         <v>6.85</v>
       </c>
-      <c r="AC33" s="32">
+      <c r="AC33" s="33">
         <v>3.17</v>
       </c>
     </row>
     <row r="34" ht="15.0" customHeight="1">
-      <c r="A34" s="28" t="s">
-        <v>451</v>
-      </c>
-      <c r="B34" s="32">
+      <c r="A34" s="29" t="s">
+        <v>452</v>
+      </c>
+      <c r="B34" s="33">
         <v>3.26</v>
       </c>
-      <c r="C34" s="32">
+      <c r="C34" s="33">
         <v>3.13</v>
       </c>
-      <c r="D34" s="32">
+      <c r="D34" s="33">
         <v>2.88</v>
       </c>
-      <c r="E34" s="32"/>
-      <c r="F34" s="32">
+      <c r="E34" s="33"/>
+      <c r="F34" s="33">
         <v>2.5</v>
       </c>
-      <c r="G34" s="32">
+      <c r="G34" s="33">
         <v>2.98</v>
       </c>
-      <c r="H34" s="32">
+      <c r="H34" s="33">
         <v>2.9</v>
       </c>
-      <c r="I34" s="32">
+      <c r="I34" s="33">
         <v>2.66</v>
       </c>
-      <c r="J34" s="32">
+      <c r="J34" s="33">
         <v>2.78</v>
       </c>
-      <c r="K34" s="32">
+      <c r="K34" s="33">
         <v>3.48</v>
       </c>
-      <c r="L34" s="32">
+      <c r="L34" s="33">
         <v>3.83</v>
       </c>
-      <c r="M34" s="32">
+      <c r="M34" s="33">
         <v>3.86</v>
       </c>
-      <c r="N34" s="32">
+      <c r="N34" s="33">
         <v>5.61</v>
       </c>
-      <c r="O34" s="32">
+      <c r="O34" s="33">
         <v>5.23</v>
       </c>
-      <c r="P34" s="32">
+      <c r="P34" s="33">
         <v>4.41</v>
       </c>
-      <c r="Q34" s="32">
+      <c r="Q34" s="33">
         <v>5.83</v>
       </c>
-      <c r="R34" s="32">
+      <c r="R34" s="33">
         <v>6.63</v>
       </c>
-      <c r="S34" s="32">
+      <c r="S34" s="33">
         <v>5.27</v>
       </c>
-      <c r="T34" s="32">
+      <c r="T34" s="33">
         <v>5.28</v>
       </c>
-      <c r="U34" s="32">
+      <c r="U34" s="33">
         <v>5.47</v>
       </c>
-      <c r="V34" s="32">
+      <c r="V34" s="33">
         <v>5.25</v>
       </c>
-      <c r="W34" s="32">
+      <c r="W34" s="33">
         <v>5.26</v>
       </c>
-      <c r="X34" s="32">
+      <c r="X34" s="33">
         <v>6.16</v>
       </c>
-      <c r="Y34" s="32">
+      <c r="Y34" s="33">
         <v>5.37</v>
       </c>
-      <c r="Z34" s="32"/>
-      <c r="AA34" s="32"/>
-      <c r="AB34" s="32"/>
-      <c r="AC34" s="32"/>
+      <c r="Z34" s="33"/>
+      <c r="AA34" s="33"/>
+      <c r="AB34" s="33"/>
+      <c r="AC34" s="33"/>
     </row>
     <row r="35" ht="15.0" customHeight="1">
-      <c r="A35" s="28" t="s">
-        <v>452</v>
-      </c>
-      <c r="B35" s="32">
+      <c r="A35" s="29" t="s">
+        <v>453</v>
+      </c>
+      <c r="B35" s="33">
         <v>5.47</v>
       </c>
-      <c r="C35" s="32">
+      <c r="C35" s="33">
         <v>6.54</v>
       </c>
-      <c r="D35" s="32">
+      <c r="D35" s="33">
         <v>7.0</v>
       </c>
-      <c r="E35" s="32"/>
-      <c r="F35" s="32">
+      <c r="E35" s="33"/>
+      <c r="F35" s="33">
         <v>0.0</v>
       </c>
-      <c r="G35" s="32">
+      <c r="G35" s="33">
         <v>4.47</v>
       </c>
-      <c r="H35" s="32">
+      <c r="H35" s="33">
         <v>5.43</v>
       </c>
-      <c r="I35" s="32">
+      <c r="I35" s="33">
         <v>5.0</v>
       </c>
-      <c r="J35" s="32">
+      <c r="J35" s="33">
         <v>3.58</v>
       </c>
-      <c r="K35" s="32">
+      <c r="K35" s="33">
         <v>3.13</v>
       </c>
-      <c r="L35" s="32">
+      <c r="L35" s="33">
         <v>3.79</v>
       </c>
-      <c r="M35" s="32">
+      <c r="M35" s="33">
         <v>3.66</v>
       </c>
-      <c r="N35" s="32">
+      <c r="N35" s="33">
         <v>10.16</v>
       </c>
-      <c r="O35" s="32">
+      <c r="O35" s="33">
         <v>12.4</v>
       </c>
-      <c r="P35" s="32">
+      <c r="P35" s="33">
         <v>2.32</v>
       </c>
-      <c r="Q35" s="32">
+      <c r="Q35" s="33">
         <v>0.0</v>
       </c>
-      <c r="R35" s="32">
+      <c r="R35" s="33">
         <v>49.69</v>
       </c>
-      <c r="S35" s="32">
+      <c r="S35" s="33">
         <v>7.8</v>
       </c>
-      <c r="T35" s="32">
+      <c r="T35" s="33">
         <v>7.26</v>
       </c>
-      <c r="U35" s="32">
+      <c r="U35" s="33">
         <v>6.36</v>
       </c>
-      <c r="V35" s="32">
+      <c r="V35" s="33">
         <v>5.14</v>
       </c>
-      <c r="W35" s="32">
+      <c r="W35" s="33">
         <v>3.68</v>
       </c>
-      <c r="X35" s="32">
+      <c r="X35" s="33">
         <v>5.83</v>
       </c>
-      <c r="Y35" s="32">
+      <c r="Y35" s="33">
         <v>6.56</v>
       </c>
-      <c r="Z35" s="32">
+      <c r="Z35" s="33">
         <v>6.83</v>
       </c>
-      <c r="AA35" s="32">
+      <c r="AA35" s="33">
         <v>5.07</v>
       </c>
-      <c r="AB35" s="32">
+      <c r="AB35" s="33">
         <v>6.85</v>
       </c>
-      <c r="AC35" s="32">
+      <c r="AC35" s="33">
         <v>3.17</v>
       </c>
     </row>
     <row r="36" ht="15.0" customHeight="1">
-      <c r="A36" s="28" t="s">
-        <v>453</v>
-      </c>
-      <c r="B36" s="32">
+      <c r="A36" s="29" t="s">
+        <v>454</v>
+      </c>
+      <c r="B36" s="33">
         <v>4.66</v>
       </c>
-      <c r="C36" s="32">
+      <c r="C36" s="33">
         <v>4.47</v>
       </c>
-      <c r="D36" s="32">
+      <c r="D36" s="33">
         <v>4.11</v>
       </c>
-      <c r="E36" s="32"/>
-      <c r="F36" s="32">
+      <c r="E36" s="33"/>
+      <c r="F36" s="33">
         <v>3.58</v>
       </c>
-      <c r="G36" s="32">
+      <c r="G36" s="33">
         <v>4.26</v>
       </c>
-      <c r="H36" s="32">
+      <c r="H36" s="33">
         <v>4.14</v>
       </c>
-      <c r="I36" s="32">
+      <c r="I36" s="33">
         <v>3.8</v>
       </c>
-      <c r="J36" s="32">
+      <c r="J36" s="33">
         <v>3.97</v>
       </c>
-      <c r="K36" s="32">
+      <c r="K36" s="33">
         <v>4.97</v>
       </c>
-      <c r="L36" s="32">
+      <c r="L36" s="33">
         <v>5.48</v>
       </c>
-      <c r="M36" s="32">
+      <c r="M36" s="33">
         <v>5.51</v>
       </c>
-      <c r="N36" s="32">
+      <c r="N36" s="33">
         <v>8.01</v>
       </c>
-      <c r="O36" s="32">
+      <c r="O36" s="33">
         <v>7.48</v>
       </c>
-      <c r="P36" s="32">
+      <c r="P36" s="33">
         <v>6.31</v>
       </c>
-      <c r="Q36" s="32">
+      <c r="Q36" s="33">
         <v>7.56</v>
       </c>
-      <c r="R36" s="32">
+      <c r="R36" s="33">
         <v>8.29</v>
       </c>
-      <c r="S36" s="32">
+      <c r="S36" s="33">
         <v>6.25</v>
       </c>
-      <c r="T36" s="32">
+      <c r="T36" s="33">
         <v>5.84</v>
       </c>
-      <c r="U36" s="32">
+      <c r="U36" s="33">
         <v>5.47</v>
       </c>
-      <c r="V36" s="32">
+      <c r="V36" s="33">
         <v>5.25</v>
       </c>
-      <c r="W36" s="32">
+      <c r="W36" s="33">
         <v>5.26</v>
       </c>
-      <c r="X36" s="32">
+      <c r="X36" s="33">
         <v>6.16</v>
       </c>
-      <c r="Y36" s="32">
+      <c r="Y36" s="33">
         <v>5.37</v>
       </c>
-      <c r="Z36" s="32"/>
-      <c r="AA36" s="32"/>
-      <c r="AB36" s="32"/>
-      <c r="AC36" s="32"/>
+      <c r="Z36" s="33"/>
+      <c r="AA36" s="33"/>
+      <c r="AB36" s="33"/>
+      <c r="AC36" s="33"/>
     </row>
     <row r="37" ht="15.0" customHeight="1">
-      <c r="A37" s="26" t="s">
-        <v>454</v>
-      </c>
-      <c r="B37" s="27"/>
-      <c r="C37" s="27"/>
-      <c r="D37" s="27"/>
-      <c r="E37" s="27"/>
-      <c r="F37" s="27"/>
-      <c r="G37" s="27"/>
-      <c r="H37" s="27"/>
-      <c r="I37" s="27"/>
-      <c r="J37" s="27"/>
-      <c r="K37" s="27"/>
-      <c r="L37" s="27"/>
-      <c r="M37" s="27"/>
-      <c r="N37" s="27"/>
-      <c r="O37" s="27"/>
-      <c r="P37" s="27"/>
-      <c r="Q37" s="27"/>
-      <c r="R37" s="27"/>
-      <c r="S37" s="27"/>
-      <c r="T37" s="27"/>
-      <c r="U37" s="27"/>
-      <c r="V37" s="27"/>
-      <c r="W37" s="27"/>
-      <c r="X37" s="27"/>
-      <c r="Y37" s="27"/>
-      <c r="Z37" s="27"/>
-      <c r="AA37" s="27"/>
-      <c r="AB37" s="27"/>
-      <c r="AC37" s="27"/>
+      <c r="A37" s="27" t="s">
+        <v>455</v>
+      </c>
+      <c r="B37" s="28"/>
+      <c r="C37" s="28"/>
+      <c r="D37" s="28"/>
+      <c r="E37" s="28"/>
+      <c r="F37" s="28"/>
+      <c r="G37" s="28"/>
+      <c r="H37" s="28"/>
+      <c r="I37" s="28"/>
+      <c r="J37" s="28"/>
+      <c r="K37" s="28"/>
+      <c r="L37" s="28"/>
+      <c r="M37" s="28"/>
+      <c r="N37" s="28"/>
+      <c r="O37" s="28"/>
+      <c r="P37" s="28"/>
+      <c r="Q37" s="28"/>
+      <c r="R37" s="28"/>
+      <c r="S37" s="28"/>
+      <c r="T37" s="28"/>
+      <c r="U37" s="28"/>
+      <c r="V37" s="28"/>
+      <c r="W37" s="28"/>
+      <c r="X37" s="28"/>
+      <c r="Y37" s="28"/>
+      <c r="Z37" s="28"/>
+      <c r="AA37" s="28"/>
+      <c r="AB37" s="28"/>
+      <c r="AC37" s="28"/>
     </row>
     <row r="38" ht="15.0" customHeight="1">
-      <c r="A38" s="28" t="s">
-        <v>455</v>
-      </c>
-      <c r="B38" s="31">
+      <c r="A38" s="29" t="s">
+        <v>456</v>
+      </c>
+      <c r="B38" s="32">
         <v>2.26</v>
       </c>
-      <c r="C38" s="31">
+      <c r="C38" s="32">
         <v>2.56</v>
       </c>
-      <c r="D38" s="31">
+      <c r="D38" s="32">
         <v>2.15</v>
       </c>
-      <c r="E38" s="31">
+      <c r="E38" s="32">
         <v>3.47</v>
       </c>
-      <c r="F38" s="31">
+      <c r="F38" s="32">
         <v>2.53</v>
       </c>
-      <c r="G38" s="31">
+      <c r="G38" s="32">
         <v>3.34</v>
       </c>
-      <c r="H38" s="31">
+      <c r="H38" s="32">
         <v>2.87</v>
       </c>
-      <c r="I38" s="31">
+      <c r="I38" s="32">
         <v>3.08</v>
       </c>
-      <c r="J38" s="31">
+      <c r="J38" s="32">
         <v>4.29</v>
       </c>
-      <c r="K38" s="31">
+      <c r="K38" s="32">
         <v>4.71</v>
       </c>
-      <c r="L38" s="31">
+      <c r="L38" s="32">
         <v>3.23</v>
       </c>
-      <c r="M38" s="31">
+      <c r="M38" s="32">
         <v>2.26</v>
       </c>
-      <c r="N38" s="31">
+      <c r="N38" s="32">
         <v>1.45</v>
       </c>
-      <c r="O38" s="31">
+      <c r="O38" s="32">
         <v>1.45</v>
       </c>
-      <c r="P38" s="31">
+      <c r="P38" s="32">
         <v>1.85</v>
       </c>
-      <c r="Q38" s="31">
+      <c r="Q38" s="32">
         <v>1.19</v>
       </c>
-      <c r="R38" s="31">
+      <c r="R38" s="32">
         <v>0.27</v>
       </c>
-      <c r="S38" s="31">
+      <c r="S38" s="32">
         <v>1.39</v>
       </c>
-      <c r="T38" s="31">
+      <c r="T38" s="32">
         <v>1.4</v>
       </c>
-      <c r="U38" s="31">
+      <c r="U38" s="32">
         <v>2.12</v>
       </c>
-      <c r="V38" s="31">
+      <c r="V38" s="32">
         <v>1.36</v>
       </c>
-      <c r="W38" s="31">
+      <c r="W38" s="32">
         <v>1.41</v>
       </c>
-      <c r="X38" s="31">
+      <c r="X38" s="32">
         <v>0.67</v>
       </c>
-      <c r="Y38" s="31">
+      <c r="Y38" s="32">
         <v>0.59</v>
       </c>
-      <c r="Z38" s="31">
+      <c r="Z38" s="32">
         <v>0.64</v>
       </c>
-      <c r="AA38" s="31">
+      <c r="AA38" s="32">
         <v>0.75</v>
       </c>
-      <c r="AB38" s="31">
+      <c r="AB38" s="32">
         <v>0.55</v>
       </c>
-      <c r="AC38" s="31">
+      <c r="AC38" s="32">
         <v>1.17</v>
       </c>
     </row>
     <row r="39" ht="15.0" customHeight="1">
-      <c r="A39" s="28" t="s">
-        <v>456</v>
-      </c>
-      <c r="B39" s="31">
+      <c r="A39" s="29" t="s">
+        <v>457</v>
+      </c>
+      <c r="B39" s="32">
         <v>2.57</v>
       </c>
-      <c r="C39" s="31">
+      <c r="C39" s="32">
         <v>2.76</v>
       </c>
-      <c r="D39" s="31">
+      <c r="D39" s="32">
         <v>2.82</v>
       </c>
-      <c r="E39" s="31">
+      <c r="E39" s="32">
         <v>3.07</v>
       </c>
-      <c r="F39" s="31">
+      <c r="F39" s="32">
         <v>3.14</v>
       </c>
-      <c r="G39" s="31">
+      <c r="G39" s="32">
         <v>3.57</v>
       </c>
-      <c r="H39" s="31">
+      <c r="H39" s="32">
         <v>3.58</v>
       </c>
-      <c r="I39" s="31">
+      <c r="I39" s="32">
         <v>3.55</v>
       </c>
-      <c r="J39" s="31">
+      <c r="J39" s="32">
         <v>3.33</v>
       </c>
-      <c r="K39" s="31">
+      <c r="K39" s="32">
         <v>2.72</v>
       </c>
-      <c r="L39" s="31">
+      <c r="L39" s="32">
         <v>2.08</v>
       </c>
-      <c r="M39" s="31">
+      <c r="M39" s="32">
         <v>1.67</v>
       </c>
-      <c r="N39" s="31">
+      <c r="N39" s="32">
         <v>1.27</v>
       </c>
-      <c r="O39" s="31">
+      <c r="O39" s="32">
         <v>1.26</v>
       </c>
-      <c r="P39" s="31">
+      <c r="P39" s="32">
         <v>1.26</v>
       </c>
-      <c r="Q39" s="31">
+      <c r="Q39" s="32">
         <v>1.28</v>
       </c>
-      <c r="R39" s="31">
+      <c r="R39" s="32">
         <v>1.31</v>
       </c>
-      <c r="S39" s="31">
+      <c r="S39" s="32">
         <v>1.52</v>
       </c>
-      <c r="T39" s="31">
+      <c r="T39" s="32">
         <v>1.37</v>
       </c>
-      <c r="U39" s="31">
+      <c r="U39" s="32">
         <v>1.2</v>
       </c>
-      <c r="V39" s="31">
+      <c r="V39" s="32">
         <v>0.93</v>
       </c>
-      <c r="W39" s="31">
+      <c r="W39" s="32">
         <v>0.8</v>
       </c>
-      <c r="X39" s="31">
+      <c r="X39" s="32">
         <v>0.64</v>
       </c>
-      <c r="Y39" s="31">
+      <c r="Y39" s="32">
         <v>0.73</v>
       </c>
-      <c r="Z39" s="29"/>
-      <c r="AA39" s="29"/>
-      <c r="AB39" s="29"/>
-      <c r="AC39" s="29"/>
+      <c r="Z39" s="30"/>
+      <c r="AA39" s="30"/>
+      <c r="AB39" s="30"/>
+      <c r="AC39" s="30"/>
     </row>
     <row r="40" ht="15.0" customHeight="1">
-      <c r="A40" s="26" t="s">
-        <v>457</v>
-      </c>
-      <c r="B40" s="27"/>
-      <c r="C40" s="27"/>
-      <c r="D40" s="27"/>
-      <c r="E40" s="27"/>
-      <c r="F40" s="27"/>
-      <c r="G40" s="27"/>
-      <c r="H40" s="27"/>
-      <c r="I40" s="27"/>
-      <c r="J40" s="27"/>
-      <c r="K40" s="27"/>
-      <c r="L40" s="27"/>
-      <c r="M40" s="27"/>
-      <c r="N40" s="27"/>
-      <c r="O40" s="27"/>
-      <c r="P40" s="27"/>
-      <c r="Q40" s="27"/>
-      <c r="R40" s="27"/>
-      <c r="S40" s="27"/>
-      <c r="T40" s="27"/>
-      <c r="U40" s="27"/>
-      <c r="V40" s="27"/>
-      <c r="W40" s="27"/>
-      <c r="X40" s="27"/>
-      <c r="Y40" s="27"/>
-      <c r="Z40" s="27"/>
-      <c r="AA40" s="27"/>
-      <c r="AB40" s="27"/>
-      <c r="AC40" s="27"/>
+      <c r="A40" s="27" t="s">
+        <v>458</v>
+      </c>
+      <c r="B40" s="28"/>
+      <c r="C40" s="28"/>
+      <c r="D40" s="28"/>
+      <c r="E40" s="28"/>
+      <c r="F40" s="28"/>
+      <c r="G40" s="28"/>
+      <c r="H40" s="28"/>
+      <c r="I40" s="28"/>
+      <c r="J40" s="28"/>
+      <c r="K40" s="28"/>
+      <c r="L40" s="28"/>
+      <c r="M40" s="28"/>
+      <c r="N40" s="28"/>
+      <c r="O40" s="28"/>
+      <c r="P40" s="28"/>
+      <c r="Q40" s="28"/>
+      <c r="R40" s="28"/>
+      <c r="S40" s="28"/>
+      <c r="T40" s="28"/>
+      <c r="U40" s="28"/>
+      <c r="V40" s="28"/>
+      <c r="W40" s="28"/>
+      <c r="X40" s="28"/>
+      <c r="Y40" s="28"/>
+      <c r="Z40" s="28"/>
+      <c r="AA40" s="28"/>
+      <c r="AB40" s="28"/>
+      <c r="AC40" s="28"/>
     </row>
     <row r="41" ht="15.0" customHeight="1">
-      <c r="A41" s="28" t="s">
-        <v>458</v>
-      </c>
-      <c r="B41" s="31">
+      <c r="A41" s="29" t="s">
+        <v>459</v>
+      </c>
+      <c r="B41" s="32">
         <v>4.74</v>
       </c>
-      <c r="C41" s="31">
+      <c r="C41" s="32">
         <v>5.22</v>
       </c>
-      <c r="D41" s="31">
+      <c r="D41" s="32">
         <v>4.76</v>
       </c>
-      <c r="E41" s="31">
+      <c r="E41" s="32">
         <v>6.85</v>
       </c>
-      <c r="F41" s="31">
+      <c r="F41" s="32">
         <v>3.86</v>
       </c>
-      <c r="G41" s="31">
+      <c r="G41" s="32">
         <v>6.25</v>
       </c>
-      <c r="H41" s="31">
+      <c r="H41" s="32">
         <v>5.96</v>
       </c>
-      <c r="I41" s="31">
+      <c r="I41" s="32">
         <v>6.15</v>
       </c>
-      <c r="J41" s="31">
+      <c r="J41" s="32">
         <v>8.26</v>
       </c>
-      <c r="K41" s="31">
+      <c r="K41" s="32">
         <v>6.83</v>
       </c>
-      <c r="L41" s="31">
+      <c r="L41" s="32">
         <v>4.23</v>
       </c>
-      <c r="M41" s="31">
+      <c r="M41" s="32">
         <v>3.0</v>
       </c>
-      <c r="N41" s="31">
+      <c r="N41" s="32">
         <v>2.11</v>
       </c>
-      <c r="O41" s="31">
+      <c r="O41" s="32">
         <v>1.76</v>
       </c>
-      <c r="P41" s="31">
+      <c r="P41" s="32">
         <v>2.42</v>
       </c>
-      <c r="Q41" s="31">
+      <c r="Q41" s="32">
         <v>1.53</v>
       </c>
-      <c r="R41" s="31">
+      <c r="R41" s="32">
         <v>0.43</v>
       </c>
-      <c r="S41" s="31">
+      <c r="S41" s="32">
         <v>2.17</v>
       </c>
-      <c r="T41" s="31">
+      <c r="T41" s="32">
         <v>1.8</v>
       </c>
-      <c r="U41" s="31">
+      <c r="U41" s="32">
         <v>2.57</v>
       </c>
-      <c r="V41" s="31">
+      <c r="V41" s="32">
         <v>1.52</v>
       </c>
-      <c r="W41" s="31">
+      <c r="W41" s="32">
         <v>1.43</v>
       </c>
-      <c r="X41" s="31">
+      <c r="X41" s="32">
         <v>0.77</v>
       </c>
-      <c r="Y41" s="31">
+      <c r="Y41" s="32">
         <v>0.64</v>
       </c>
-      <c r="Z41" s="31">
+      <c r="Z41" s="32">
         <v>0.71</v>
       </c>
-      <c r="AA41" s="31">
+      <c r="AA41" s="32">
         <v>0.83</v>
       </c>
-      <c r="AB41" s="31">
+      <c r="AB41" s="32">
         <v>0.59</v>
       </c>
-      <c r="AC41" s="31">
+      <c r="AC41" s="32">
         <v>1.22</v>
       </c>
     </row>
     <row r="42" ht="15.0" customHeight="1">
-      <c r="A42" s="28" t="s">
-        <v>459</v>
-      </c>
-      <c r="B42" s="31">
+      <c r="A42" s="29" t="s">
+        <v>460</v>
+      </c>
+      <c r="B42" s="32">
         <v>5.05</v>
       </c>
-      <c r="C42" s="31">
+      <c r="C42" s="32">
         <v>5.3</v>
       </c>
-      <c r="D42" s="31">
+      <c r="D42" s="32">
         <v>5.4</v>
       </c>
-      <c r="E42" s="31">
+      <c r="E42" s="32">
         <v>5.67</v>
       </c>
-      <c r="F42" s="31">
+      <c r="F42" s="32">
         <v>5.73</v>
       </c>
-      <c r="G42" s="31">
+      <c r="G42" s="32">
         <v>6.65</v>
       </c>
-      <c r="H42" s="31">
+      <c r="H42" s="32">
         <v>6.25</v>
       </c>
-      <c r="I42" s="31">
+      <c r="I42" s="32">
         <v>5.65</v>
       </c>
-      <c r="J42" s="31">
+      <c r="J42" s="32">
         <v>4.95</v>
       </c>
-      <c r="K42" s="31">
+      <c r="K42" s="32">
         <v>3.67</v>
       </c>
-      <c r="L42" s="31">
+      <c r="L42" s="32">
         <v>2.74</v>
       </c>
-      <c r="M42" s="31">
+      <c r="M42" s="32">
         <v>2.19</v>
       </c>
-      <c r="N42" s="31">
+      <c r="N42" s="32">
         <v>1.72</v>
       </c>
-      <c r="O42" s="31">
+      <c r="O42" s="32">
         <v>1.74</v>
       </c>
-      <c r="P42" s="31">
+      <c r="P42" s="32">
         <v>1.75</v>
       </c>
-      <c r="Q42" s="31">
+      <c r="Q42" s="32">
         <v>1.75</v>
       </c>
-      <c r="R42" s="31">
+      <c r="R42" s="32">
         <v>1.74</v>
       </c>
-      <c r="S42" s="31">
+      <c r="S42" s="32">
         <v>1.87</v>
       </c>
-      <c r="T42" s="31">
+      <c r="T42" s="32">
         <v>1.59</v>
       </c>
-      <c r="U42" s="31">
+      <c r="U42" s="32">
         <v>1.34</v>
       </c>
-      <c r="V42" s="31">
+      <c r="V42" s="32">
         <v>1.02</v>
       </c>
-      <c r="W42" s="31">
+      <c r="W42" s="32">
         <v>0.87</v>
       </c>
-      <c r="X42" s="31">
+      <c r="X42" s="32">
         <v>0.71</v>
       </c>
-      <c r="Y42" s="31">
+      <c r="Y42" s="32">
         <v>0.79</v>
       </c>
-      <c r="Z42" s="29"/>
-      <c r="AA42" s="29"/>
-      <c r="AB42" s="29"/>
-      <c r="AC42" s="29"/>
+      <c r="Z42" s="30"/>
+      <c r="AA42" s="30"/>
+      <c r="AB42" s="30"/>
+      <c r="AC42" s="30"/>
     </row>
     <row r="43" ht="15.0" customHeight="1">
-      <c r="A43" s="26" t="s">
-        <v>460</v>
-      </c>
-      <c r="B43" s="27"/>
-      <c r="C43" s="27"/>
-      <c r="D43" s="27"/>
-      <c r="E43" s="27"/>
-      <c r="F43" s="27"/>
-      <c r="G43" s="27"/>
-      <c r="H43" s="27"/>
-      <c r="I43" s="27"/>
-      <c r="J43" s="27"/>
-      <c r="K43" s="27"/>
-      <c r="L43" s="27"/>
-      <c r="M43" s="27"/>
-      <c r="N43" s="27"/>
-      <c r="O43" s="27"/>
-      <c r="P43" s="27"/>
-      <c r="Q43" s="27"/>
-      <c r="R43" s="27"/>
-      <c r="S43" s="27"/>
-      <c r="T43" s="27"/>
-      <c r="U43" s="27"/>
-      <c r="V43" s="27"/>
-      <c r="W43" s="27"/>
-      <c r="X43" s="27"/>
-      <c r="Y43" s="27"/>
-      <c r="Z43" s="27"/>
-      <c r="AA43" s="27"/>
-      <c r="AB43" s="27"/>
-      <c r="AC43" s="27"/>
+      <c r="A43" s="27" t="s">
+        <v>461</v>
+      </c>
+      <c r="B43" s="28"/>
+      <c r="C43" s="28"/>
+      <c r="D43" s="28"/>
+      <c r="E43" s="28"/>
+      <c r="F43" s="28"/>
+      <c r="G43" s="28"/>
+      <c r="H43" s="28"/>
+      <c r="I43" s="28"/>
+      <c r="J43" s="28"/>
+      <c r="K43" s="28"/>
+      <c r="L43" s="28"/>
+      <c r="M43" s="28"/>
+      <c r="N43" s="28"/>
+      <c r="O43" s="28"/>
+      <c r="P43" s="28"/>
+      <c r="Q43" s="28"/>
+      <c r="R43" s="28"/>
+      <c r="S43" s="28"/>
+      <c r="T43" s="28"/>
+      <c r="U43" s="28"/>
+      <c r="V43" s="28"/>
+      <c r="W43" s="28"/>
+      <c r="X43" s="28"/>
+      <c r="Y43" s="28"/>
+      <c r="Z43" s="28"/>
+      <c r="AA43" s="28"/>
+      <c r="AB43" s="28"/>
+      <c r="AC43" s="28"/>
     </row>
     <row r="44" ht="15.0" customHeight="1">
-      <c r="A44" s="28" t="s">
-        <v>461</v>
-      </c>
-      <c r="B44" s="31">
+      <c r="A44" s="29" t="s">
+        <v>462</v>
+      </c>
+      <c r="B44" s="32">
         <v>0.29</v>
       </c>
-      <c r="C44" s="31">
+      <c r="C44" s="32">
         <v>0.32</v>
       </c>
-      <c r="D44" s="31">
+      <c r="D44" s="32">
         <v>0.3</v>
       </c>
-      <c r="E44" s="31">
+      <c r="E44" s="32">
         <v>0.44</v>
       </c>
-      <c r="F44" s="31">
+      <c r="F44" s="32">
         <v>0.34</v>
       </c>
-      <c r="G44" s="31">
+      <c r="G44" s="32">
         <v>0.36</v>
       </c>
-      <c r="H44" s="31">
+      <c r="H44" s="32">
         <v>0.29</v>
       </c>
-      <c r="I44" s="31">
+      <c r="I44" s="32">
         <v>0.3</v>
       </c>
-      <c r="J44" s="31">
+      <c r="J44" s="32">
         <v>0.45</v>
       </c>
-      <c r="K44" s="31">
+      <c r="K44" s="32">
         <v>0.48</v>
       </c>
-      <c r="L44" s="31">
+      <c r="L44" s="32">
         <v>0.33</v>
       </c>
-      <c r="M44" s="31">
+      <c r="M44" s="32">
         <v>0.23</v>
       </c>
-      <c r="N44" s="31">
+      <c r="N44" s="32">
         <v>0.13</v>
       </c>
-      <c r="O44" s="31">
+      <c r="O44" s="32">
         <v>0.13</v>
       </c>
-      <c r="P44" s="31">
+      <c r="P44" s="32">
         <v>0.2</v>
       </c>
-      <c r="Q44" s="31">
+      <c r="Q44" s="32">
         <v>0.13</v>
       </c>
-      <c r="R44" s="31">
+      <c r="R44" s="32">
         <v>0.02</v>
       </c>
-      <c r="S44" s="31">
+      <c r="S44" s="32">
         <v>0.14</v>
       </c>
-      <c r="T44" s="31">
+      <c r="T44" s="32">
         <v>0.18</v>
       </c>
-      <c r="U44" s="31">
+      <c r="U44" s="32">
         <v>0.23</v>
       </c>
-      <c r="V44" s="31">
+      <c r="V44" s="32">
         <v>0.18</v>
       </c>
-      <c r="W44" s="31">
+      <c r="W44" s="32">
         <v>0.12</v>
       </c>
-      <c r="X44" s="31">
+      <c r="X44" s="32">
         <v>0.06</v>
       </c>
-      <c r="Y44" s="31">
+      <c r="Y44" s="32">
         <v>0.06</v>
       </c>
-      <c r="Z44" s="31">
+      <c r="Z44" s="32">
         <v>0.06</v>
       </c>
-      <c r="AA44" s="31">
+      <c r="AA44" s="32">
         <v>0.07</v>
       </c>
-      <c r="AB44" s="31">
+      <c r="AB44" s="32">
         <v>0.06</v>
       </c>
-      <c r="AC44" s="31">
+      <c r="AC44" s="32">
         <v>0.12</v>
       </c>
     </row>
     <row r="45" ht="15.0" customHeight="1">
-      <c r="A45" s="28" t="s">
-        <v>462</v>
-      </c>
-      <c r="B45" s="31">
+      <c r="A45" s="29" t="s">
+        <v>463</v>
+      </c>
+      <c r="B45" s="32">
         <v>0.33</v>
       </c>
-      <c r="C45" s="31">
+      <c r="C45" s="32">
         <v>0.35</v>
       </c>
-      <c r="D45" s="31">
+      <c r="D45" s="32">
         <v>0.35</v>
       </c>
-      <c r="E45" s="31">
+      <c r="E45" s="32">
         <v>0.35</v>
       </c>
-      <c r="F45" s="31">
+      <c r="F45" s="32">
         <v>0.35</v>
       </c>
-      <c r="G45" s="31">
+      <c r="G45" s="32">
         <v>0.37</v>
       </c>
-      <c r="H45" s="31">
+      <c r="H45" s="32">
         <v>0.36</v>
       </c>
-      <c r="I45" s="31">
+      <c r="I45" s="32">
         <v>0.36</v>
       </c>
-      <c r="J45" s="31">
+      <c r="J45" s="32">
         <v>0.33</v>
       </c>
-      <c r="K45" s="31">
+      <c r="K45" s="32">
         <v>0.27</v>
       </c>
-      <c r="L45" s="31">
+      <c r="L45" s="32">
         <v>0.21</v>
       </c>
-      <c r="M45" s="31">
+      <c r="M45" s="32">
         <v>0.17</v>
       </c>
-      <c r="N45" s="31">
+      <c r="N45" s="32">
         <v>0.12</v>
       </c>
-      <c r="O45" s="31">
+      <c r="O45" s="32">
         <v>0.12</v>
       </c>
-      <c r="P45" s="31">
+      <c r="P45" s="32">
         <v>0.13</v>
       </c>
-      <c r="Q45" s="31">
+      <c r="Q45" s="32">
         <v>0.13</v>
       </c>
-      <c r="R45" s="31">
+      <c r="R45" s="32">
         <v>0.14</v>
       </c>
-      <c r="S45" s="31">
+      <c r="S45" s="32">
         <v>0.17</v>
       </c>
-      <c r="T45" s="31">
+      <c r="T45" s="32">
         <v>0.15</v>
       </c>
-      <c r="U45" s="31">
+      <c r="U45" s="32">
         <v>0.12</v>
       </c>
-      <c r="V45" s="31">
+      <c r="V45" s="32">
         <v>0.09</v>
       </c>
-      <c r="W45" s="31">
+      <c r="W45" s="32">
         <v>0.07</v>
       </c>
-      <c r="X45" s="31">
+      <c r="X45" s="32">
         <v>0.06</v>
       </c>
-      <c r="Y45" s="31">
+      <c r="Y45" s="32">
         <v>0.07</v>
       </c>
-      <c r="Z45" s="29"/>
-      <c r="AA45" s="29"/>
-      <c r="AB45" s="29"/>
-      <c r="AC45" s="29"/>
+      <c r="Z45" s="30"/>
+      <c r="AA45" s="30"/>
+      <c r="AB45" s="30"/>
+      <c r="AC45" s="30"/>
     </row>
     <row r="46" ht="15.0" customHeight="1">
-      <c r="A46" s="26" t="s">
-        <v>463</v>
-      </c>
-      <c r="B46" s="27"/>
-      <c r="C46" s="27"/>
-      <c r="D46" s="27"/>
-      <c r="E46" s="27"/>
-      <c r="F46" s="27"/>
-      <c r="G46" s="27"/>
-      <c r="H46" s="27"/>
-      <c r="I46" s="27"/>
-      <c r="J46" s="27"/>
-      <c r="K46" s="27"/>
-      <c r="L46" s="27"/>
-      <c r="M46" s="27"/>
-      <c r="N46" s="27"/>
-      <c r="O46" s="27"/>
-      <c r="P46" s="27"/>
-      <c r="Q46" s="27"/>
-      <c r="R46" s="27"/>
-      <c r="S46" s="27"/>
-      <c r="T46" s="27"/>
-      <c r="U46" s="27"/>
-      <c r="V46" s="27"/>
-      <c r="W46" s="27"/>
-      <c r="X46" s="27"/>
-      <c r="Y46" s="27"/>
-      <c r="Z46" s="27"/>
-      <c r="AA46" s="27"/>
-      <c r="AB46" s="27"/>
-      <c r="AC46" s="27"/>
+      <c r="A46" s="27" t="s">
+        <v>464</v>
+      </c>
+      <c r="B46" s="28"/>
+      <c r="C46" s="28"/>
+      <c r="D46" s="28"/>
+      <c r="E46" s="28"/>
+      <c r="F46" s="28"/>
+      <c r="G46" s="28"/>
+      <c r="H46" s="28"/>
+      <c r="I46" s="28"/>
+      <c r="J46" s="28"/>
+      <c r="K46" s="28"/>
+      <c r="L46" s="28"/>
+      <c r="M46" s="28"/>
+      <c r="N46" s="28"/>
+      <c r="O46" s="28"/>
+      <c r="P46" s="28"/>
+      <c r="Q46" s="28"/>
+      <c r="R46" s="28"/>
+      <c r="S46" s="28"/>
+      <c r="T46" s="28"/>
+      <c r="U46" s="28"/>
+      <c r="V46" s="28"/>
+      <c r="W46" s="28"/>
+      <c r="X46" s="28"/>
+      <c r="Y46" s="28"/>
+      <c r="Z46" s="28"/>
+      <c r="AA46" s="28"/>
+      <c r="AB46" s="28"/>
+      <c r="AC46" s="28"/>
     </row>
     <row r="47" ht="15.0" customHeight="1">
-      <c r="A47" s="28" t="s">
-        <v>464</v>
-      </c>
-      <c r="B47" s="31">
+      <c r="A47" s="29" t="s">
+        <v>465</v>
+      </c>
+      <c r="B47" s="32">
         <v>33.41</v>
       </c>
-      <c r="C47" s="29"/>
-      <c r="D47" s="29"/>
-      <c r="E47" s="31">
+      <c r="C47" s="30"/>
+      <c r="D47" s="30"/>
+      <c r="E47" s="32">
         <v>21.46</v>
       </c>
-      <c r="F47" s="31">
+      <c r="F47" s="32">
         <v>6.42</v>
       </c>
-      <c r="G47" s="29"/>
-      <c r="H47" s="29"/>
-      <c r="I47" s="29"/>
-      <c r="J47" s="29"/>
-      <c r="K47" s="29"/>
-      <c r="L47" s="31">
+      <c r="G47" s="30"/>
+      <c r="H47" s="30"/>
+      <c r="I47" s="30"/>
+      <c r="J47" s="30"/>
+      <c r="K47" s="30"/>
+      <c r="L47" s="32">
         <v>91.62</v>
       </c>
-      <c r="M47" s="29"/>
-      <c r="N47" s="31">
+      <c r="M47" s="30"/>
+      <c r="N47" s="32">
         <v>31.7</v>
       </c>
-      <c r="O47" s="31">
+      <c r="O47" s="32">
         <v>5.05</v>
       </c>
-      <c r="P47" s="29"/>
-      <c r="Q47" s="31">
+      <c r="P47" s="30"/>
+      <c r="Q47" s="32">
         <v>3.39</v>
       </c>
-      <c r="R47" s="31">
+      <c r="R47" s="32">
         <v>0.99</v>
       </c>
-      <c r="S47" s="29"/>
-      <c r="T47" s="31">
+      <c r="S47" s="30"/>
+      <c r="T47" s="32">
         <v>14.48</v>
       </c>
-      <c r="U47" s="29"/>
-      <c r="V47" s="29"/>
-      <c r="W47" s="31">
+      <c r="U47" s="30"/>
+      <c r="V47" s="30"/>
+      <c r="W47" s="32">
         <v>15.67</v>
       </c>
-      <c r="X47" s="31">
+      <c r="X47" s="32">
         <v>6.61</v>
       </c>
-      <c r="Y47" s="31">
+      <c r="Y47" s="32">
         <v>1.54</v>
       </c>
-      <c r="Z47" s="29"/>
-      <c r="AA47" s="31">
+      <c r="Z47" s="30"/>
+      <c r="AA47" s="32">
         <v>1.92</v>
       </c>
-      <c r="AB47" s="29"/>
-      <c r="AC47" s="31">
+      <c r="AB47" s="30"/>
+      <c r="AC47" s="32">
         <v>6.42</v>
       </c>
     </row>
     <row r="48" ht="15.0" customHeight="1">
-      <c r="A48" s="28" t="s">
-        <v>465</v>
-      </c>
-      <c r="B48" s="31">
+      <c r="A48" s="29" t="s">
+        <v>466</v>
+      </c>
+      <c r="B48" s="32">
         <v>51.66</v>
       </c>
-      <c r="C48" s="30">
+      <c r="C48" s="31">
         <v>155.94</v>
       </c>
-      <c r="D48" s="30">
+      <c r="D48" s="31">
         <v>161.14</v>
       </c>
-      <c r="E48" s="31">
+      <c r="E48" s="32">
         <v>78.63</v>
       </c>
-      <c r="F48" s="29"/>
-      <c r="G48" s="29"/>
-      <c r="H48" s="29"/>
-      <c r="I48" s="29"/>
-      <c r="J48" s="29"/>
-      <c r="K48" s="29"/>
-      <c r="L48" s="30">
+      <c r="F48" s="30"/>
+      <c r="G48" s="30"/>
+      <c r="H48" s="30"/>
+      <c r="I48" s="30"/>
+      <c r="J48" s="30"/>
+      <c r="K48" s="30"/>
+      <c r="L48" s="31">
         <v>588.81</v>
       </c>
-      <c r="M48" s="31">
+      <c r="M48" s="32">
         <v>28.78</v>
       </c>
-      <c r="N48" s="31">
+      <c r="N48" s="32">
         <v>7.65</v>
       </c>
-      <c r="O48" s="29"/>
-      <c r="P48" s="29"/>
-      <c r="Q48" s="29"/>
-      <c r="R48" s="29"/>
-      <c r="S48" s="29"/>
-      <c r="T48" s="31">
+      <c r="O48" s="30"/>
+      <c r="P48" s="30"/>
+      <c r="Q48" s="30"/>
+      <c r="R48" s="30"/>
+      <c r="S48" s="30"/>
+      <c r="T48" s="32">
         <v>30.77</v>
       </c>
-      <c r="U48" s="31">
+      <c r="U48" s="32">
         <v>12.01</v>
       </c>
-      <c r="V48" s="31">
+      <c r="V48" s="32">
         <v>13.59</v>
       </c>
-      <c r="W48" s="31">
+      <c r="W48" s="32">
         <v>5.45</v>
       </c>
-      <c r="X48" s="31">
+      <c r="X48" s="32">
         <v>6.76</v>
       </c>
-      <c r="Y48" s="31">
+      <c r="Y48" s="32">
         <v>6.69</v>
       </c>
-      <c r="Z48" s="29"/>
-      <c r="AA48" s="29"/>
-      <c r="AB48" s="29"/>
-      <c r="AC48" s="29"/>
+      <c r="Z48" s="30"/>
+      <c r="AA48" s="30"/>
+      <c r="AB48" s="30"/>
+      <c r="AC48" s="30"/>
     </row>
     <row r="49" ht="15.0" customHeight="1">
-      <c r="A49" s="26" t="s">
-        <v>466</v>
-      </c>
-      <c r="B49" s="27"/>
-      <c r="C49" s="27"/>
-      <c r="D49" s="27"/>
-      <c r="E49" s="27"/>
-      <c r="F49" s="27"/>
-      <c r="G49" s="27"/>
-      <c r="H49" s="27"/>
-      <c r="I49" s="27"/>
-      <c r="J49" s="27"/>
-      <c r="K49" s="27"/>
-      <c r="L49" s="27"/>
-      <c r="M49" s="27"/>
-      <c r="N49" s="27"/>
-      <c r="O49" s="27"/>
-      <c r="P49" s="27"/>
-      <c r="Q49" s="27"/>
-      <c r="R49" s="27"/>
-      <c r="S49" s="27"/>
-      <c r="T49" s="27"/>
-      <c r="U49" s="27"/>
-      <c r="V49" s="27"/>
-      <c r="W49" s="27"/>
-      <c r="X49" s="27"/>
-      <c r="Y49" s="27"/>
-      <c r="Z49" s="27"/>
-      <c r="AA49" s="27"/>
-      <c r="AB49" s="27"/>
-      <c r="AC49" s="27"/>
+      <c r="A49" s="27" t="s">
+        <v>467</v>
+      </c>
+      <c r="B49" s="28"/>
+      <c r="C49" s="28"/>
+      <c r="D49" s="28"/>
+      <c r="E49" s="28"/>
+      <c r="F49" s="28"/>
+      <c r="G49" s="28"/>
+      <c r="H49" s="28"/>
+      <c r="I49" s="28"/>
+      <c r="J49" s="28"/>
+      <c r="K49" s="28"/>
+      <c r="L49" s="28"/>
+      <c r="M49" s="28"/>
+      <c r="N49" s="28"/>
+      <c r="O49" s="28"/>
+      <c r="P49" s="28"/>
+      <c r="Q49" s="28"/>
+      <c r="R49" s="28"/>
+      <c r="S49" s="28"/>
+      <c r="T49" s="28"/>
+      <c r="U49" s="28"/>
+      <c r="V49" s="28"/>
+      <c r="W49" s="28"/>
+      <c r="X49" s="28"/>
+      <c r="Y49" s="28"/>
+      <c r="Z49" s="28"/>
+      <c r="AA49" s="28"/>
+      <c r="AB49" s="28"/>
+      <c r="AC49" s="28"/>
     </row>
     <row r="50" ht="15.0" customHeight="1">
-      <c r="A50" s="28" t="s">
-        <v>467</v>
-      </c>
-      <c r="B50" s="31">
+      <c r="A50" s="29" t="s">
+        <v>468</v>
+      </c>
+      <c r="B50" s="32">
         <v>5.19</v>
       </c>
-      <c r="C50" s="31">
+      <c r="C50" s="32">
         <v>5.24</v>
       </c>
-      <c r="D50" s="31">
+      <c r="D50" s="32">
         <v>3.63</v>
       </c>
-      <c r="E50" s="31">
+      <c r="E50" s="32">
         <v>5.75</v>
       </c>
-      <c r="F50" s="31">
+      <c r="F50" s="32">
         <v>4.81</v>
       </c>
-      <c r="G50" s="31">
+      <c r="G50" s="32">
         <v>5.49</v>
       </c>
-      <c r="H50" s="31">
+      <c r="H50" s="32">
         <v>5.93</v>
       </c>
-      <c r="I50" s="31">
+      <c r="I50" s="32">
         <v>6.12</v>
       </c>
-      <c r="J50" s="31">
+      <c r="J50" s="32">
         <v>9.1</v>
       </c>
-      <c r="K50" s="31">
+      <c r="K50" s="32">
         <v>8.71</v>
       </c>
-      <c r="L50" s="31">
+      <c r="L50" s="32">
         <v>7.73</v>
       </c>
-      <c r="M50" s="31">
+      <c r="M50" s="32">
         <v>6.59</v>
       </c>
-      <c r="N50" s="31">
+      <c r="N50" s="32">
         <v>4.42</v>
       </c>
-      <c r="O50" s="31">
+      <c r="O50" s="32">
         <v>3.17</v>
       </c>
-      <c r="P50" s="31">
+      <c r="P50" s="32">
         <v>4.49</v>
       </c>
-      <c r="Q50" s="31">
+      <c r="Q50" s="32">
         <v>4.24</v>
       </c>
-      <c r="R50" s="31">
+      <c r="R50" s="32">
         <v>1.42</v>
       </c>
-      <c r="S50" s="31">
+      <c r="S50" s="32">
         <v>5.48</v>
       </c>
-      <c r="T50" s="31">
+      <c r="T50" s="32">
         <v>7.41</v>
       </c>
-      <c r="U50" s="31">
+      <c r="U50" s="32">
         <v>7.14</v>
       </c>
-      <c r="V50" s="31">
+      <c r="V50" s="32">
         <v>5.25</v>
       </c>
-      <c r="W50" s="31">
+      <c r="W50" s="32">
         <v>3.92</v>
       </c>
-      <c r="X50" s="31">
+      <c r="X50" s="32">
         <v>2.13</v>
       </c>
-      <c r="Y50" s="31">
+      <c r="Y50" s="32">
         <v>1.83</v>
       </c>
-      <c r="Z50" s="31">
+      <c r="Z50" s="32">
         <v>2.39</v>
       </c>
-      <c r="AA50" s="31">
+      <c r="AA50" s="32">
         <v>4.8</v>
       </c>
-      <c r="AB50" s="31">
+      <c r="AB50" s="32">
         <v>2.53</v>
       </c>
-      <c r="AC50" s="31">
+      <c r="AC50" s="32">
         <v>3.67</v>
       </c>
     </row>
     <row r="51" ht="15.0" customHeight="1">
-      <c r="A51" s="28" t="s">
-        <v>468</v>
-      </c>
-      <c r="B51" s="31">
+      <c r="A51" s="29" t="s">
+        <v>469</v>
+      </c>
+      <c r="B51" s="32">
         <v>4.88</v>
       </c>
-      <c r="C51" s="31">
+      <c r="C51" s="32">
         <v>4.91</v>
       </c>
-      <c r="D51" s="31">
+      <c r="D51" s="32">
         <v>4.96</v>
       </c>
-      <c r="E51" s="31">
+      <c r="E51" s="32">
         <v>5.56</v>
       </c>
-      <c r="F51" s="31">
+      <c r="F51" s="32">
         <v>6.02</v>
       </c>
-      <c r="G51" s="31">
+      <c r="G51" s="32">
         <v>6.81</v>
       </c>
-      <c r="H51" s="31">
+      <c r="H51" s="32">
         <v>7.39</v>
       </c>
-      <c r="I51" s="31">
+      <c r="I51" s="32">
         <v>7.7</v>
       </c>
-      <c r="J51" s="31">
+      <c r="J51" s="32">
         <v>7.78</v>
       </c>
-      <c r="K51" s="31">
+      <c r="K51" s="32">
         <v>6.45</v>
       </c>
-      <c r="L51" s="31">
+      <c r="L51" s="32">
         <v>5.3</v>
       </c>
-      <c r="M51" s="31">
+      <c r="M51" s="32">
         <v>4.54</v>
       </c>
-      <c r="N51" s="31">
+      <c r="N51" s="32">
         <v>3.74</v>
       </c>
-      <c r="O51" s="31">
+      <c r="O51" s="32">
         <v>3.92</v>
       </c>
-      <c r="P51" s="31">
+      <c r="P51" s="32">
         <v>4.74</v>
       </c>
-      <c r="Q51" s="31">
+      <c r="Q51" s="32">
         <v>5.35</v>
       </c>
-      <c r="R51" s="31">
+      <c r="R51" s="32">
         <v>5.56</v>
       </c>
-      <c r="S51" s="31">
+      <c r="S51" s="32">
         <v>5.75</v>
       </c>
-      <c r="T51" s="31">
+      <c r="T51" s="32">
         <v>4.97</v>
       </c>
-      <c r="U51" s="31">
+      <c r="U51" s="32">
         <v>3.9</v>
       </c>
-      <c r="V51" s="31">
+      <c r="V51" s="32">
         <v>3.07</v>
       </c>
-      <c r="W51" s="31">
+      <c r="W51" s="32">
         <v>2.78</v>
       </c>
-      <c r="X51" s="31">
+      <c r="X51" s="32">
         <v>2.45</v>
       </c>
-      <c r="Y51" s="31">
+      <c r="Y51" s="32">
         <v>2.81</v>
       </c>
-      <c r="Z51" s="29"/>
-      <c r="AA51" s="29"/>
-      <c r="AB51" s="29"/>
-      <c r="AC51" s="29"/>
+      <c r="Z51" s="30"/>
+      <c r="AA51" s="30"/>
+      <c r="AB51" s="30"/>
+      <c r="AC51" s="30"/>
     </row>
     <row r="52" ht="15.0" customHeight="1">
-      <c r="A52" s="26" t="s">
-        <v>469</v>
-      </c>
-      <c r="B52" s="27"/>
-      <c r="C52" s="27"/>
-      <c r="D52" s="27"/>
-      <c r="E52" s="27"/>
-      <c r="F52" s="27"/>
-      <c r="G52" s="27"/>
-      <c r="H52" s="27"/>
-      <c r="I52" s="27"/>
-      <c r="J52" s="27"/>
-      <c r="K52" s="27"/>
-      <c r="L52" s="27"/>
-      <c r="M52" s="27"/>
-      <c r="N52" s="27"/>
-      <c r="O52" s="27"/>
-      <c r="P52" s="27"/>
-      <c r="Q52" s="27"/>
-      <c r="R52" s="27"/>
-      <c r="S52" s="27"/>
-      <c r="T52" s="27"/>
-      <c r="U52" s="27"/>
-      <c r="V52" s="27"/>
-      <c r="W52" s="27"/>
-      <c r="X52" s="27"/>
-      <c r="Y52" s="27"/>
-      <c r="Z52" s="27"/>
-      <c r="AA52" s="27"/>
-      <c r="AB52" s="27"/>
-      <c r="AC52" s="27"/>
+      <c r="A52" s="27" t="s">
+        <v>470</v>
+      </c>
+      <c r="B52" s="28"/>
+      <c r="C52" s="28"/>
+      <c r="D52" s="28"/>
+      <c r="E52" s="28"/>
+      <c r="F52" s="28"/>
+      <c r="G52" s="28"/>
+      <c r="H52" s="28"/>
+      <c r="I52" s="28"/>
+      <c r="J52" s="28"/>
+      <c r="K52" s="28"/>
+      <c r="L52" s="28"/>
+      <c r="M52" s="28"/>
+      <c r="N52" s="28"/>
+      <c r="O52" s="28"/>
+      <c r="P52" s="28"/>
+      <c r="Q52" s="28"/>
+      <c r="R52" s="28"/>
+      <c r="S52" s="28"/>
+      <c r="T52" s="28"/>
+      <c r="U52" s="28"/>
+      <c r="V52" s="28"/>
+      <c r="W52" s="28"/>
+      <c r="X52" s="28"/>
+      <c r="Y52" s="28"/>
+      <c r="Z52" s="28"/>
+      <c r="AA52" s="28"/>
+      <c r="AB52" s="28"/>
+      <c r="AC52" s="28"/>
     </row>
     <row r="53" ht="15.0" customHeight="1">
-      <c r="A53" s="28" t="s">
-        <v>470</v>
-      </c>
-      <c r="B53" s="31">
+      <c r="A53" s="29" t="s">
+        <v>471</v>
+      </c>
+      <c r="B53" s="32">
         <v>16.88</v>
       </c>
-      <c r="C53" s="31">
+      <c r="C53" s="32">
         <v>13.33</v>
       </c>
-      <c r="D53" s="31">
+      <c r="D53" s="32">
         <v>6.56</v>
       </c>
-      <c r="E53" s="31">
+      <c r="E53" s="32">
         <v>10.75</v>
       </c>
-      <c r="F53" s="31">
+      <c r="F53" s="32">
         <v>10.32</v>
       </c>
-      <c r="G53" s="31">
+      <c r="G53" s="32">
         <v>13.29</v>
       </c>
-      <c r="H53" s="31">
+      <c r="H53" s="32">
         <v>11.4</v>
       </c>
-      <c r="I53" s="31">
+      <c r="I53" s="32">
         <v>11.84</v>
       </c>
-      <c r="J53" s="31">
+      <c r="J53" s="32">
         <v>16.31</v>
       </c>
-      <c r="K53" s="31">
+      <c r="K53" s="32">
         <v>13.37</v>
       </c>
-      <c r="L53" s="31">
+      <c r="L53" s="32">
         <v>13.38</v>
       </c>
-      <c r="M53" s="31">
+      <c r="M53" s="32">
         <v>14.0</v>
       </c>
-      <c r="N53" s="31">
+      <c r="N53" s="32">
         <v>14.83</v>
       </c>
-      <c r="O53" s="31">
+      <c r="O53" s="32">
         <v>5.83</v>
       </c>
-      <c r="P53" s="31">
+      <c r="P53" s="32">
         <v>8.1</v>
       </c>
-      <c r="Q53" s="31">
+      <c r="Q53" s="32">
         <v>15.48</v>
       </c>
-      <c r="R53" s="29"/>
-      <c r="S53" s="31">
+      <c r="R53" s="30"/>
+      <c r="S53" s="32">
         <v>20.37</v>
       </c>
-      <c r="T53" s="31">
+      <c r="T53" s="32">
         <v>28.14</v>
       </c>
-      <c r="U53" s="31">
+      <c r="U53" s="32">
         <v>20.51</v>
       </c>
-      <c r="V53" s="31">
+      <c r="V53" s="32">
         <v>9.31</v>
       </c>
-      <c r="W53" s="31">
+      <c r="W53" s="32">
         <v>8.33</v>
       </c>
-      <c r="X53" s="31">
+      <c r="X53" s="32">
         <v>5.85</v>
       </c>
-      <c r="Y53" s="31">
+      <c r="Y53" s="32">
         <v>2.78</v>
       </c>
-      <c r="Z53" s="31">
+      <c r="Z53" s="32">
         <v>1.14</v>
       </c>
-      <c r="AA53" s="31">
+      <c r="AA53" s="32">
         <v>3.96</v>
       </c>
-      <c r="AB53" s="31">
+      <c r="AB53" s="32">
         <v>1.34</v>
       </c>
-      <c r="AC53" s="31">
+      <c r="AC53" s="32">
         <v>5.64</v>
       </c>
     </row>
     <row r="54" ht="15.0" customHeight="1">
-      <c r="A54" s="28" t="s">
-        <v>471</v>
-      </c>
-      <c r="B54" s="31">
+      <c r="A54" s="29" t="s">
+        <v>472</v>
+      </c>
+      <c r="B54" s="32">
         <v>10.63</v>
       </c>
-      <c r="C54" s="31">
+      <c r="C54" s="32">
         <v>10.24</v>
       </c>
-      <c r="D54" s="31">
+      <c r="D54" s="32">
         <v>9.84</v>
       </c>
-      <c r="E54" s="31">
+      <c r="E54" s="32">
         <v>11.36</v>
       </c>
-      <c r="F54" s="31">
+      <c r="F54" s="32">
         <v>12.42</v>
       </c>
-      <c r="G54" s="31">
+      <c r="G54" s="32">
         <v>13.19</v>
       </c>
-      <c r="H54" s="31">
+      <c r="H54" s="32">
         <v>13.19</v>
       </c>
-      <c r="I54" s="31">
+      <c r="I54" s="32">
         <v>13.75</v>
       </c>
-      <c r="J54" s="31">
+      <c r="J54" s="32">
         <v>14.4</v>
       </c>
-      <c r="K54" s="31">
+      <c r="K54" s="32">
         <v>12.03</v>
       </c>
-      <c r="L54" s="31">
+      <c r="L54" s="32">
         <v>10.55</v>
       </c>
-      <c r="M54" s="31">
+      <c r="M54" s="32">
         <v>10.04</v>
       </c>
-      <c r="N54" s="31">
+      <c r="N54" s="32">
         <v>10.68</v>
       </c>
-      <c r="O54" s="31">
+      <c r="O54" s="32">
         <v>11.3</v>
       </c>
-      <c r="P54" s="31">
+      <c r="P54" s="32">
         <v>17.82</v>
       </c>
-      <c r="Q54" s="31">
+      <c r="Q54" s="32">
         <v>30.22</v>
       </c>
-      <c r="R54" s="31">
+      <c r="R54" s="32">
         <v>23.25</v>
       </c>
-      <c r="S54" s="31">
+      <c r="S54" s="32">
         <v>14.96</v>
       </c>
-      <c r="T54" s="31">
+      <c r="T54" s="32">
         <v>12.27</v>
       </c>
-      <c r="U54" s="31">
+      <c r="U54" s="32">
         <v>8.08</v>
       </c>
-      <c r="V54" s="31">
+      <c r="V54" s="32">
         <v>4.07</v>
       </c>
-      <c r="W54" s="31">
+      <c r="W54" s="32">
         <v>3.31</v>
       </c>
-      <c r="X54" s="31">
+      <c r="X54" s="32">
         <v>2.24</v>
       </c>
-      <c r="Y54" s="31">
+      <c r="Y54" s="32">
         <v>2.32</v>
       </c>
-      <c r="Z54" s="29"/>
-      <c r="AA54" s="29"/>
-      <c r="AB54" s="29"/>
-      <c r="AC54" s="29"/>
+      <c r="Z54" s="30"/>
+      <c r="AA54" s="30"/>
+      <c r="AB54" s="30"/>
+      <c r="AC54" s="30"/>
     </row>
     <row r="55" ht="15.0" customHeight="1">
-      <c r="A55" s="26" t="s">
-        <v>472</v>
-      </c>
-      <c r="B55" s="27"/>
-      <c r="C55" s="27"/>
-      <c r="D55" s="27"/>
-      <c r="E55" s="27"/>
-      <c r="F55" s="27"/>
-      <c r="G55" s="27"/>
-      <c r="H55" s="27"/>
-      <c r="I55" s="27"/>
-      <c r="J55" s="27"/>
-      <c r="K55" s="27"/>
-      <c r="L55" s="27"/>
-      <c r="M55" s="27"/>
-      <c r="N55" s="27"/>
-      <c r="O55" s="27"/>
-      <c r="P55" s="27"/>
-      <c r="Q55" s="27"/>
-      <c r="R55" s="27"/>
-      <c r="S55" s="27"/>
-      <c r="T55" s="27"/>
-      <c r="U55" s="27"/>
-      <c r="V55" s="27"/>
-      <c r="W55" s="27"/>
-      <c r="X55" s="27"/>
-      <c r="Y55" s="27"/>
-      <c r="Z55" s="27"/>
-      <c r="AA55" s="27"/>
-      <c r="AB55" s="27"/>
-      <c r="AC55" s="27"/>
+      <c r="A55" s="27" t="s">
+        <v>473</v>
+      </c>
+      <c r="B55" s="28"/>
+      <c r="C55" s="28"/>
+      <c r="D55" s="28"/>
+      <c r="E55" s="28"/>
+      <c r="F55" s="28"/>
+      <c r="G55" s="28"/>
+      <c r="H55" s="28"/>
+      <c r="I55" s="28"/>
+      <c r="J55" s="28"/>
+      <c r="K55" s="28"/>
+      <c r="L55" s="28"/>
+      <c r="M55" s="28"/>
+      <c r="N55" s="28"/>
+      <c r="O55" s="28"/>
+      <c r="P55" s="28"/>
+      <c r="Q55" s="28"/>
+      <c r="R55" s="28"/>
+      <c r="S55" s="28"/>
+      <c r="T55" s="28"/>
+      <c r="U55" s="28"/>
+      <c r="V55" s="28"/>
+      <c r="W55" s="28"/>
+      <c r="X55" s="28"/>
+      <c r="Y55" s="28"/>
+      <c r="Z55" s="28"/>
+      <c r="AA55" s="28"/>
+      <c r="AB55" s="28"/>
+      <c r="AC55" s="28"/>
     </row>
     <row r="56" ht="15.0" customHeight="1">
-      <c r="A56" s="28" t="s">
-        <v>473</v>
-      </c>
-      <c r="B56" s="31">
+      <c r="A56" s="29" t="s">
+        <v>474</v>
+      </c>
+      <c r="B56" s="32">
         <v>12.41</v>
       </c>
-      <c r="C56" s="31">
+      <c r="C56" s="32">
         <v>13.03</v>
       </c>
-      <c r="D56" s="31">
+      <c r="D56" s="32">
         <v>8.39</v>
       </c>
-      <c r="E56" s="31">
+      <c r="E56" s="32">
         <v>10.17</v>
       </c>
-      <c r="F56" s="31">
+      <c r="F56" s="32">
         <v>8.96</v>
       </c>
-      <c r="G56" s="31">
+      <c r="G56" s="32">
         <v>11.81</v>
       </c>
-      <c r="H56" s="31">
+      <c r="H56" s="32">
         <v>10.26</v>
       </c>
-      <c r="I56" s="31">
+      <c r="I56" s="32">
         <v>11.0</v>
       </c>
-      <c r="J56" s="31">
+      <c r="J56" s="32">
         <v>15.83</v>
       </c>
-      <c r="K56" s="31">
+      <c r="K56" s="32">
         <v>13.21</v>
       </c>
-      <c r="L56" s="31">
+      <c r="L56" s="32">
         <v>13.44</v>
       </c>
-      <c r="M56" s="31">
+      <c r="M56" s="32">
         <v>12.81</v>
       </c>
-      <c r="N56" s="31">
+      <c r="N56" s="32">
         <v>10.66</v>
       </c>
-      <c r="O56" s="31">
+      <c r="O56" s="32">
         <v>5.7</v>
       </c>
-      <c r="P56" s="31">
+      <c r="P56" s="32">
         <v>7.87</v>
       </c>
-      <c r="Q56" s="31">
+      <c r="Q56" s="32">
         <v>15.48</v>
       </c>
-      <c r="R56" s="29"/>
-      <c r="S56" s="31">
+      <c r="R56" s="30"/>
+      <c r="S56" s="32">
         <v>20.37</v>
       </c>
-      <c r="T56" s="31">
+      <c r="T56" s="32">
         <v>28.14</v>
       </c>
-      <c r="U56" s="31">
+      <c r="U56" s="32">
         <v>20.51</v>
       </c>
-      <c r="V56" s="31">
+      <c r="V56" s="32">
         <v>9.31</v>
       </c>
-      <c r="W56" s="31">
+      <c r="W56" s="32">
         <v>8.33</v>
       </c>
-      <c r="X56" s="31">
+      <c r="X56" s="32">
         <v>5.85</v>
       </c>
-      <c r="Y56" s="31">
+      <c r="Y56" s="32">
         <v>3.54</v>
       </c>
-      <c r="Z56" s="31">
+      <c r="Z56" s="32">
         <v>6.39</v>
       </c>
-      <c r="AA56" s="30">
+      <c r="AA56" s="31">
         <v>296.09</v>
       </c>
-      <c r="AB56" s="31">
+      <c r="AB56" s="32">
         <v>6.66</v>
       </c>
-      <c r="AC56" s="31">
+      <c r="AC56" s="32">
         <v>6.42</v>
       </c>
     </row>
     <row r="57" ht="15.0" customHeight="1">
-      <c r="A57" s="28" t="s">
-        <v>474</v>
-      </c>
-      <c r="B57" s="31">
+      <c r="A57" s="29" t="s">
+        <v>475</v>
+      </c>
+      <c r="B57" s="32">
         <v>2.57</v>
       </c>
-      <c r="C57" s="31">
+      <c r="C57" s="32">
         <v>2.76</v>
       </c>
-      <c r="D57" s="31">
+      <c r="D57" s="32">
         <v>2.82</v>
       </c>
-      <c r="E57" s="31">
+      <c r="E57" s="32">
         <v>3.07</v>
       </c>
-      <c r="F57" s="31">
+      <c r="F57" s="32">
         <v>3.14</v>
       </c>
-      <c r="G57" s="31">
+      <c r="G57" s="32">
         <v>3.57</v>
       </c>
-      <c r="H57" s="31">
+      <c r="H57" s="32">
         <v>3.58</v>
       </c>
-      <c r="I57" s="31">
+      <c r="I57" s="32">
         <v>3.55</v>
       </c>
-      <c r="J57" s="31">
+      <c r="J57" s="32">
         <v>3.33</v>
       </c>
-      <c r="K57" s="31">
+      <c r="K57" s="32">
         <v>2.72</v>
       </c>
-      <c r="L57" s="31">
+      <c r="L57" s="32">
         <v>2.08</v>
       </c>
-      <c r="M57" s="31">
+      <c r="M57" s="32">
         <v>1.67</v>
       </c>
-      <c r="N57" s="31">
+      <c r="N57" s="32">
         <v>1.27</v>
       </c>
-      <c r="O57" s="31">
+      <c r="O57" s="32">
         <v>1.26</v>
       </c>
-      <c r="P57" s="31">
+      <c r="P57" s="32">
         <v>1.26</v>
       </c>
-      <c r="Q57" s="31">
+      <c r="Q57" s="32">
         <v>1.28</v>
       </c>
-      <c r="R57" s="31">
+      <c r="R57" s="32">
         <v>1.31</v>
       </c>
-      <c r="S57" s="31">
+      <c r="S57" s="32">
         <v>1.52</v>
       </c>
-      <c r="T57" s="31">
+      <c r="T57" s="32">
         <v>1.37</v>
       </c>
-      <c r="U57" s="31">
+      <c r="U57" s="32">
         <v>1.2</v>
       </c>
-      <c r="V57" s="31">
+      <c r="V57" s="32">
         <v>0.93</v>
       </c>
-      <c r="W57" s="31">
+      <c r="W57" s="32">
         <v>0.8</v>
       </c>
-      <c r="X57" s="31">
+      <c r="X57" s="32">
         <v>0.64</v>
       </c>
-      <c r="Y57" s="31">
+      <c r="Y57" s="32">
         <v>0.73</v>
       </c>
-      <c r="Z57" s="29"/>
-      <c r="AA57" s="29"/>
-      <c r="AB57" s="29"/>
-      <c r="AC57" s="29"/>
+      <c r="Z57" s="30"/>
+      <c r="AA57" s="30"/>
+      <c r="AB57" s="30"/>
+      <c r="AC57" s="30"/>
     </row>
     <row r="58" ht="15.0" customHeight="1">
-      <c r="A58" s="26" t="s">
-        <v>475</v>
-      </c>
-      <c r="B58" s="27"/>
-      <c r="C58" s="27"/>
-      <c r="D58" s="27"/>
-      <c r="E58" s="27"/>
-      <c r="F58" s="27"/>
-      <c r="G58" s="27"/>
-      <c r="H58" s="27"/>
-      <c r="I58" s="27"/>
-      <c r="J58" s="27"/>
-      <c r="K58" s="27"/>
-      <c r="L58" s="27"/>
-      <c r="M58" s="27"/>
-      <c r="N58" s="27"/>
-      <c r="O58" s="27"/>
-      <c r="P58" s="27"/>
-      <c r="Q58" s="27"/>
-      <c r="R58" s="27"/>
-      <c r="S58" s="27"/>
-      <c r="T58" s="27"/>
-      <c r="U58" s="27"/>
-      <c r="V58" s="27"/>
-      <c r="W58" s="27"/>
-      <c r="X58" s="27"/>
-      <c r="Y58" s="27"/>
-      <c r="Z58" s="27"/>
-      <c r="AA58" s="27"/>
-      <c r="AB58" s="27"/>
-      <c r="AC58" s="27"/>
+      <c r="A58" s="27" t="s">
+        <v>476</v>
+      </c>
+      <c r="B58" s="28"/>
+      <c r="C58" s="28"/>
+      <c r="D58" s="28"/>
+      <c r="E58" s="28"/>
+      <c r="F58" s="28"/>
+      <c r="G58" s="28"/>
+      <c r="H58" s="28"/>
+      <c r="I58" s="28"/>
+      <c r="J58" s="28"/>
+      <c r="K58" s="28"/>
+      <c r="L58" s="28"/>
+      <c r="M58" s="28"/>
+      <c r="N58" s="28"/>
+      <c r="O58" s="28"/>
+      <c r="P58" s="28"/>
+      <c r="Q58" s="28"/>
+      <c r="R58" s="28"/>
+      <c r="S58" s="28"/>
+      <c r="T58" s="28"/>
+      <c r="U58" s="28"/>
+      <c r="V58" s="28"/>
+      <c r="W58" s="28"/>
+      <c r="X58" s="28"/>
+      <c r="Y58" s="28"/>
+      <c r="Z58" s="28"/>
+      <c r="AA58" s="28"/>
+      <c r="AB58" s="28"/>
+      <c r="AC58" s="28"/>
     </row>
     <row r="59" ht="15.0" customHeight="1">
-      <c r="A59" s="28" t="s">
-        <v>476</v>
-      </c>
-      <c r="B59" s="34">
+      <c r="A59" s="29" t="s">
+        <v>477</v>
+      </c>
+      <c r="B59" s="35">
         <v>-0.58</v>
       </c>
-      <c r="C59" s="34">
+      <c r="C59" s="35">
         <v>-0.32</v>
       </c>
-      <c r="D59" s="31">
+      <c r="D59" s="32">
         <v>0.39</v>
       </c>
-      <c r="E59" s="31">
+      <c r="E59" s="32">
         <v>0.21</v>
       </c>
-      <c r="F59" s="31">
+      <c r="F59" s="32">
         <v>0.45</v>
       </c>
-      <c r="G59" s="31">
+      <c r="G59" s="32">
         <v>1.31</v>
       </c>
-      <c r="H59" s="31">
+      <c r="H59" s="32">
         <v>1.51</v>
       </c>
-      <c r="I59" s="31">
+      <c r="I59" s="32">
         <v>2.28</v>
       </c>
-      <c r="J59" s="34">
+      <c r="J59" s="35">
         <v>-1.55</v>
       </c>
-      <c r="K59" s="31">
+      <c r="K59" s="32">
         <v>0.22</v>
       </c>
-      <c r="L59" s="31">
+      <c r="L59" s="32">
         <v>0.26</v>
       </c>
-      <c r="M59" s="31">
+      <c r="M59" s="32">
         <v>0.16</v>
       </c>
-      <c r="N59" s="34">
+      <c r="N59" s="35">
         <v>-0.24</v>
       </c>
-      <c r="O59" s="31">
+      <c r="O59" s="32">
         <v>1.5</v>
       </c>
-      <c r="P59" s="31">
+      <c r="P59" s="32">
         <v>0.03</v>
       </c>
-      <c r="Q59" s="31">
+      <c r="Q59" s="32">
         <v>0.08</v>
       </c>
-      <c r="R59" s="29"/>
-      <c r="S59" s="31">
+      <c r="R59" s="30"/>
+      <c r="S59" s="32">
         <v>0.72</v>
       </c>
-      <c r="T59" s="34">
+      <c r="T59" s="35">
         <v>-0.88</v>
       </c>
-      <c r="U59" s="34">
+      <c r="U59" s="35">
         <v>-0.53</v>
       </c>
-      <c r="V59" s="31">
+      <c r="V59" s="32">
         <v>1.18</v>
       </c>
-      <c r="W59" s="31">
+      <c r="W59" s="32">
         <v>0.46</v>
       </c>
-      <c r="X59" s="34">
+      <c r="X59" s="35">
         <v>-0.14</v>
       </c>
-      <c r="Y59" s="34">
+      <c r="Y59" s="35">
         <v>-0.05</v>
       </c>
-      <c r="Z59" s="31">
+      <c r="Z59" s="32">
         <v>0.01</v>
       </c>
-      <c r="AA59" s="34">
+      <c r="AA59" s="35">
         <v>-0.07</v>
       </c>
-      <c r="AB59" s="31">
+      <c r="AB59" s="32">
         <v>0.01</v>
       </c>
-      <c r="AC59" s="29"/>
+      <c r="AC59" s="30"/>
     </row>
     <row r="60" ht="15.0" customHeight="1">
-      <c r="A60" s="28" t="s">
-        <v>477</v>
-      </c>
-      <c r="B60" s="34">
+      <c r="A60" s="29" t="s">
+        <v>478</v>
+      </c>
+      <c r="B60" s="35">
         <v>-4.77</v>
       </c>
-      <c r="C60" s="31">
+      <c r="C60" s="32">
         <v>1.5</v>
       </c>
-      <c r="D60" s="31">
+      <c r="D60" s="32">
         <v>0.47</v>
       </c>
-      <c r="E60" s="31">
+      <c r="E60" s="32">
         <v>0.62</v>
       </c>
-      <c r="F60" s="31">
+      <c r="F60" s="32">
         <v>1.92</v>
       </c>
-      <c r="G60" s="31">
+      <c r="G60" s="32">
         <v>1.05</v>
       </c>
-      <c r="H60" s="31">
+      <c r="H60" s="32">
         <v>0.66</v>
       </c>
-      <c r="I60" s="31">
+      <c r="I60" s="32">
         <v>0.41</v>
       </c>
-      <c r="J60" s="31">
+      <c r="J60" s="32">
         <v>1.58</v>
       </c>
-      <c r="K60" s="31">
+      <c r="K60" s="32">
         <v>0.97</v>
       </c>
-      <c r="L60" s="31">
+      <c r="L60" s="32">
         <v>0.33</v>
       </c>
-      <c r="M60" s="29"/>
-      <c r="N60" s="31">
+      <c r="M60" s="30"/>
+      <c r="N60" s="32">
         <v>2.32</v>
       </c>
-      <c r="O60" s="31">
+      <c r="O60" s="32">
         <v>0.34</v>
       </c>
-      <c r="P60" s="31">
+      <c r="P60" s="32">
         <v>0.79</v>
       </c>
-      <c r="Q60" s="34">
+      <c r="Q60" s="35">
         <v>-2.21</v>
       </c>
-      <c r="R60" s="29"/>
-      <c r="S60" s="34">
+      <c r="R60" s="30"/>
+      <c r="S60" s="35">
         <v>-2.04</v>
       </c>
-      <c r="T60" s="34">
+      <c r="T60" s="35">
         <v>-0.58</v>
       </c>
-      <c r="U60" s="34">
+      <c r="U60" s="35">
         <v>-0.3</v>
       </c>
-      <c r="V60" s="30">
+      <c r="V60" s="31">
         <v>153.05</v>
       </c>
-      <c r="W60" s="34">
+      <c r="W60" s="35">
         <v>-0.21</v>
       </c>
-      <c r="X60" s="34">
+      <c r="X60" s="35">
         <v>-0.43</v>
       </c>
-      <c r="Y60" s="29"/>
-      <c r="Z60" s="29"/>
-      <c r="AA60" s="29"/>
-      <c r="AB60" s="29"/>
-      <c r="AC60" s="29"/>
+      <c r="Y60" s="30"/>
+      <c r="Z60" s="30"/>
+      <c r="AA60" s="30"/>
+      <c r="AB60" s="30"/>
+      <c r="AC60" s="30"/>
     </row>
     <row r="61" ht="15.0" customHeight="1">
-      <c r="A61" s="26" t="s">
-        <v>478</v>
-      </c>
-      <c r="B61" s="27"/>
-      <c r="C61" s="27"/>
-      <c r="D61" s="27"/>
-      <c r="E61" s="27"/>
-      <c r="F61" s="27"/>
-      <c r="G61" s="27"/>
-      <c r="H61" s="27"/>
-      <c r="I61" s="27"/>
-      <c r="J61" s="27"/>
-      <c r="K61" s="27"/>
-      <c r="L61" s="27"/>
-      <c r="M61" s="27"/>
-      <c r="N61" s="27"/>
-      <c r="O61" s="27"/>
-      <c r="P61" s="27"/>
-      <c r="Q61" s="27"/>
-      <c r="R61" s="27"/>
-      <c r="S61" s="27"/>
-      <c r="T61" s="27"/>
-      <c r="U61" s="27"/>
-      <c r="V61" s="27"/>
-      <c r="W61" s="27"/>
-      <c r="X61" s="27"/>
-      <c r="Y61" s="27"/>
-      <c r="Z61" s="27"/>
-      <c r="AA61" s="27"/>
-      <c r="AB61" s="27"/>
-      <c r="AC61" s="27"/>
+      <c r="A61" s="27" t="s">
+        <v>479</v>
+      </c>
+      <c r="B61" s="28"/>
+      <c r="C61" s="28"/>
+      <c r="D61" s="28"/>
+      <c r="E61" s="28"/>
+      <c r="F61" s="28"/>
+      <c r="G61" s="28"/>
+      <c r="H61" s="28"/>
+      <c r="I61" s="28"/>
+      <c r="J61" s="28"/>
+      <c r="K61" s="28"/>
+      <c r="L61" s="28"/>
+      <c r="M61" s="28"/>
+      <c r="N61" s="28"/>
+      <c r="O61" s="28"/>
+      <c r="P61" s="28"/>
+      <c r="Q61" s="28"/>
+      <c r="R61" s="28"/>
+      <c r="S61" s="28"/>
+      <c r="T61" s="28"/>
+      <c r="U61" s="28"/>
+      <c r="V61" s="28"/>
+      <c r="W61" s="28"/>
+      <c r="X61" s="28"/>
+      <c r="Y61" s="28"/>
+      <c r="Z61" s="28"/>
+      <c r="AA61" s="28"/>
+      <c r="AB61" s="28"/>
+      <c r="AC61" s="28"/>
     </row>
     <row r="62" ht="15.0" customHeight="1">
-      <c r="A62" s="28" t="s">
-        <v>479</v>
-      </c>
-      <c r="B62" s="31">
+      <c r="A62" s="29" t="s">
+        <v>480</v>
+      </c>
+      <c r="B62" s="32">
         <v>0.57</v>
       </c>
-      <c r="C62" s="31">
+      <c r="C62" s="32">
         <v>0.58</v>
       </c>
-      <c r="D62" s="31">
+      <c r="D62" s="32">
         <v>0.51</v>
       </c>
-      <c r="E62" s="31">
+      <c r="E62" s="32">
         <v>0.63</v>
       </c>
-      <c r="F62" s="31">
+      <c r="F62" s="32">
         <v>0.52</v>
       </c>
-      <c r="G62" s="31">
+      <c r="G62" s="32">
         <v>0.63</v>
       </c>
-      <c r="H62" s="31">
+      <c r="H62" s="32">
         <v>0.47</v>
       </c>
-      <c r="I62" s="31">
+      <c r="I62" s="32">
         <v>0.46</v>
       </c>
-      <c r="J62" s="31">
+      <c r="J62" s="32">
         <v>0.6</v>
       </c>
-      <c r="K62" s="31">
+      <c r="K62" s="32">
         <v>0.54</v>
       </c>
-      <c r="L62" s="31">
+      <c r="L62" s="32">
         <v>0.33</v>
       </c>
-      <c r="M62" s="31">
+      <c r="M62" s="32">
         <v>0.27</v>
       </c>
-      <c r="N62" s="31">
+      <c r="N62" s="32">
         <v>0.18</v>
       </c>
-      <c r="O62" s="31">
+      <c r="O62" s="32">
         <v>0.15</v>
       </c>
-      <c r="P62" s="31">
+      <c r="P62" s="32">
         <v>0.21</v>
       </c>
-      <c r="Q62" s="31">
+      <c r="Q62" s="32">
         <v>0.13</v>
       </c>
-      <c r="R62" s="31">
+      <c r="R62" s="32">
         <v>0.08</v>
       </c>
-      <c r="S62" s="31">
+      <c r="S62" s="32">
         <v>0.22</v>
       </c>
-      <c r="T62" s="31">
+      <c r="T62" s="32">
         <v>0.19</v>
       </c>
-      <c r="U62" s="31">
+      <c r="U62" s="32">
         <v>0.3</v>
       </c>
-      <c r="V62" s="31">
+      <c r="V62" s="32">
         <v>0.2</v>
       </c>
-      <c r="W62" s="31">
+      <c r="W62" s="32">
         <v>0.23</v>
       </c>
-      <c r="X62" s="31">
+      <c r="X62" s="32">
         <v>0.23</v>
       </c>
-      <c r="Y62" s="31">
+      <c r="Y62" s="32">
         <v>0.2</v>
       </c>
-      <c r="Z62" s="31">
+      <c r="Z62" s="32">
         <v>0.25</v>
       </c>
-      <c r="AA62" s="31">
+      <c r="AA62" s="32">
         <v>0.26</v>
       </c>
-      <c r="AB62" s="31">
+      <c r="AB62" s="32">
         <v>0.27</v>
       </c>
-      <c r="AC62" s="31">
+      <c r="AC62" s="32">
         <v>0.35</v>
       </c>
     </row>
     <row r="63" ht="15.0" customHeight="1">
-      <c r="A63" s="28" t="s">
-        <v>480</v>
-      </c>
-      <c r="B63" s="31">
+      <c r="A63" s="29" t="s">
+        <v>481</v>
+      </c>
+      <c r="B63" s="32">
         <v>0.57</v>
       </c>
-      <c r="C63" s="31">
+      <c r="C63" s="32">
         <v>0.58</v>
       </c>
-      <c r="D63" s="31">
+      <c r="D63" s="32">
         <v>0.55</v>
       </c>
-      <c r="E63" s="31">
+      <c r="E63" s="32">
         <v>0.55</v>
       </c>
-      <c r="F63" s="31">
+      <c r="F63" s="32">
         <v>0.54</v>
       </c>
-      <c r="G63" s="31">
+      <c r="G63" s="32">
         <v>0.54</v>
       </c>
-      <c r="H63" s="31">
+      <c r="H63" s="32">
         <v>0.49</v>
       </c>
-      <c r="I63" s="31">
+      <c r="I63" s="32">
         <v>0.46</v>
       </c>
-      <c r="J63" s="31">
+      <c r="J63" s="32">
         <v>0.4</v>
       </c>
-      <c r="K63" s="31">
+      <c r="K63" s="32">
         <v>0.3</v>
       </c>
-      <c r="L63" s="31">
+      <c r="L63" s="32">
         <v>0.23</v>
       </c>
-      <c r="M63" s="31">
+      <c r="M63" s="32">
         <v>0.19</v>
       </c>
-      <c r="N63" s="31">
+      <c r="N63" s="32">
         <v>0.15</v>
       </c>
-      <c r="O63" s="31">
+      <c r="O63" s="32">
         <v>0.16</v>
       </c>
-      <c r="P63" s="31">
+      <c r="P63" s="32">
         <v>0.17</v>
       </c>
-      <c r="Q63" s="31">
+      <c r="Q63" s="32">
         <v>0.18</v>
       </c>
-      <c r="R63" s="31">
+      <c r="R63" s="32">
         <v>0.2</v>
       </c>
-      <c r="S63" s="31">
+      <c r="S63" s="32">
         <v>0.23</v>
       </c>
-      <c r="T63" s="31">
+      <c r="T63" s="32">
         <v>0.23</v>
       </c>
-      <c r="U63" s="31">
+      <c r="U63" s="32">
         <v>0.23</v>
       </c>
-      <c r="V63" s="31">
+      <c r="V63" s="32">
         <v>0.22</v>
       </c>
-      <c r="W63" s="31">
+      <c r="W63" s="32">
         <v>0.23</v>
       </c>
-      <c r="X63" s="31">
+      <c r="X63" s="32">
         <v>0.24</v>
       </c>
-      <c r="Y63" s="31">
+      <c r="Y63" s="32">
         <v>0.26</v>
       </c>
-      <c r="Z63" s="29"/>
-      <c r="AA63" s="29"/>
-      <c r="AB63" s="29"/>
-      <c r="AC63" s="29"/>
+      <c r="Z63" s="30"/>
+      <c r="AA63" s="30"/>
+      <c r="AB63" s="30"/>
+      <c r="AC63" s="30"/>
     </row>
     <row r="64" ht="15.0" customHeight="1">
-      <c r="A64" s="26" t="s">
-        <v>481</v>
-      </c>
-      <c r="B64" s="27"/>
-      <c r="C64" s="27"/>
-      <c r="D64" s="27"/>
-      <c r="E64" s="27"/>
-      <c r="F64" s="27"/>
-      <c r="G64" s="27"/>
-      <c r="H64" s="27"/>
-      <c r="I64" s="27"/>
-      <c r="J64" s="27"/>
-      <c r="K64" s="27"/>
-      <c r="L64" s="27"/>
-      <c r="M64" s="27"/>
-      <c r="N64" s="27"/>
-      <c r="O64" s="27"/>
-      <c r="P64" s="27"/>
-      <c r="Q64" s="27"/>
-      <c r="R64" s="27"/>
-      <c r="S64" s="27"/>
-      <c r="T64" s="27"/>
-      <c r="U64" s="27"/>
-      <c r="V64" s="27"/>
-      <c r="W64" s="27"/>
-      <c r="X64" s="27"/>
-      <c r="Y64" s="27"/>
-      <c r="Z64" s="27"/>
-      <c r="AA64" s="27"/>
-      <c r="AB64" s="27"/>
-      <c r="AC64" s="27"/>
+      <c r="A64" s="27" t="s">
+        <v>482</v>
+      </c>
+      <c r="B64" s="28"/>
+      <c r="C64" s="28"/>
+      <c r="D64" s="28"/>
+      <c r="E64" s="28"/>
+      <c r="F64" s="28"/>
+      <c r="G64" s="28"/>
+      <c r="H64" s="28"/>
+      <c r="I64" s="28"/>
+      <c r="J64" s="28"/>
+      <c r="K64" s="28"/>
+      <c r="L64" s="28"/>
+      <c r="M64" s="28"/>
+      <c r="N64" s="28"/>
+      <c r="O64" s="28"/>
+      <c r="P64" s="28"/>
+      <c r="Q64" s="28"/>
+      <c r="R64" s="28"/>
+      <c r="S64" s="28"/>
+      <c r="T64" s="28"/>
+      <c r="U64" s="28"/>
+      <c r="V64" s="28"/>
+      <c r="W64" s="28"/>
+      <c r="X64" s="28"/>
+      <c r="Y64" s="28"/>
+      <c r="Z64" s="28"/>
+      <c r="AA64" s="28"/>
+      <c r="AB64" s="28"/>
+      <c r="AC64" s="28"/>
     </row>
     <row r="65" ht="15.0" customHeight="1">
-      <c r="A65" s="28" t="s">
-        <v>482</v>
-      </c>
-      <c r="B65" s="31">
+      <c r="A65" s="29" t="s">
+        <v>483</v>
+      </c>
+      <c r="B65" s="32">
         <v>7.6</v>
       </c>
-      <c r="C65" s="31">
+      <c r="C65" s="32">
         <v>7.84</v>
       </c>
-      <c r="D65" s="31">
+      <c r="D65" s="32">
         <v>5.95</v>
       </c>
-      <c r="E65" s="31">
+      <c r="E65" s="32">
         <v>6.79</v>
       </c>
-      <c r="F65" s="31">
+      <c r="F65" s="32">
         <v>5.96</v>
       </c>
-      <c r="G65" s="31">
+      <c r="G65" s="32">
         <v>7.92</v>
       </c>
-      <c r="H65" s="31">
+      <c r="H65" s="32">
         <v>7.81</v>
       </c>
-      <c r="I65" s="31">
+      <c r="I65" s="32">
         <v>7.92</v>
       </c>
-      <c r="J65" s="31">
+      <c r="J65" s="32">
         <v>10.5</v>
       </c>
-      <c r="K65" s="31">
+      <c r="K65" s="32">
         <v>8.32</v>
       </c>
-      <c r="L65" s="31">
+      <c r="L65" s="32">
         <v>6.94</v>
       </c>
-      <c r="M65" s="31">
+      <c r="M65" s="32">
         <v>6.71</v>
       </c>
-      <c r="N65" s="31">
+      <c r="N65" s="32">
         <v>4.46</v>
       </c>
-      <c r="O65" s="31">
+      <c r="O65" s="32">
         <v>3.17</v>
       </c>
-      <c r="P65" s="31">
+      <c r="P65" s="32">
         <v>0.24</v>
       </c>
-      <c r="Q65" s="31">
+      <c r="Q65" s="32">
         <v>0.15</v>
       </c>
-      <c r="R65" s="31">
+      <c r="R65" s="32">
         <v>6.73</v>
       </c>
-      <c r="S65" s="31">
+      <c r="S65" s="32">
         <v>7.57</v>
       </c>
-      <c r="T65" s="31">
+      <c r="T65" s="32">
         <v>6.45</v>
       </c>
-      <c r="U65" s="31">
+      <c r="U65" s="32">
         <v>8.24</v>
       </c>
-      <c r="V65" s="31">
+      <c r="V65" s="32">
         <v>4.7</v>
       </c>
-      <c r="W65" s="31">
+      <c r="W65" s="32">
         <v>5.58</v>
       </c>
-      <c r="X65" s="31">
+      <c r="X65" s="32">
         <v>5.87</v>
       </c>
-      <c r="Y65" s="31">
+      <c r="Y65" s="32">
         <v>4.27</v>
       </c>
-      <c r="Z65" s="31">
+      <c r="Z65" s="32">
         <v>7.45</v>
       </c>
-      <c r="AA65" s="29"/>
-      <c r="AB65" s="31">
+      <c r="AA65" s="30"/>
+      <c r="AB65" s="32">
         <v>8.74</v>
       </c>
-      <c r="AC65" s="31">
+      <c r="AC65" s="32">
         <v>8.17</v>
       </c>
     </row>
     <row r="66" ht="15.0" customHeight="1">
-      <c r="A66" s="28" t="s">
-        <v>483</v>
-      </c>
-      <c r="B66" s="31">
+      <c r="A66" s="29" t="s">
+        <v>484</v>
+      </c>
+      <c r="B66" s="32">
         <v>6.84</v>
       </c>
-      <c r="C66" s="31">
+      <c r="C66" s="32">
         <v>6.86</v>
       </c>
-      <c r="D66" s="31">
+      <c r="D66" s="32">
         <v>6.76</v>
       </c>
-      <c r="E66" s="31">
+      <c r="E66" s="32">
         <v>7.14</v>
       </c>
-      <c r="F66" s="31">
+      <c r="F66" s="32">
         <v>7.73</v>
       </c>
-      <c r="G66" s="31">
+      <c r="G66" s="32">
         <v>8.39</v>
       </c>
-      <c r="H66" s="31">
+      <c r="H66" s="32">
         <v>8.36</v>
       </c>
-      <c r="I66" s="31">
+      <c r="I66" s="32">
         <v>8.31</v>
       </c>
-      <c r="J66" s="31">
+      <c r="J66" s="32">
         <v>7.9</v>
       </c>
-      <c r="K66" s="31">
+      <c r="K66" s="32">
         <v>6.21</v>
       </c>
-      <c r="L66" s="31">
+      <c r="L66" s="32">
         <v>1.16</v>
       </c>
-      <c r="M66" s="31">
+      <c r="M66" s="32">
         <v>0.56</v>
       </c>
-      <c r="N66" s="31">
+      <c r="N66" s="32">
         <v>0.44</v>
       </c>
-      <c r="O66" s="31">
+      <c r="O66" s="32">
         <v>0.45</v>
       </c>
-      <c r="P66" s="31">
+      <c r="P66" s="32">
         <v>0.46</v>
       </c>
-      <c r="Q66" s="31">
+      <c r="Q66" s="32">
         <v>0.95</v>
       </c>
-      <c r="R66" s="31">
+      <c r="R66" s="32">
         <v>6.69</v>
       </c>
-      <c r="S66" s="31">
+      <c r="S66" s="32">
         <v>6.4</v>
       </c>
-      <c r="T66" s="31">
+      <c r="T66" s="32">
         <v>6.06</v>
       </c>
-      <c r="U66" s="31">
+      <c r="U66" s="32">
         <v>5.54</v>
       </c>
-      <c r="V66" s="31">
+      <c r="V66" s="32">
         <v>5.51</v>
       </c>
-      <c r="W66" s="29"/>
-      <c r="X66" s="29"/>
-      <c r="Y66" s="29"/>
-      <c r="Z66" s="29"/>
-      <c r="AA66" s="29"/>
-      <c r="AB66" s="29"/>
-      <c r="AC66" s="29"/>
+      <c r="W66" s="30"/>
+      <c r="X66" s="30"/>
+      <c r="Y66" s="30"/>
+      <c r="Z66" s="30"/>
+      <c r="AA66" s="30"/>
+      <c r="AB66" s="30"/>
+      <c r="AC66" s="30"/>
     </row>
     <row r="67" ht="15.0" customHeight="1">
-      <c r="A67" s="26" t="s">
-        <v>484</v>
-      </c>
-      <c r="B67" s="27"/>
-      <c r="C67" s="27"/>
-      <c r="D67" s="27"/>
-      <c r="E67" s="27"/>
-      <c r="F67" s="27"/>
-      <c r="G67" s="27"/>
-      <c r="H67" s="27"/>
-      <c r="I67" s="27"/>
-      <c r="J67" s="27"/>
-      <c r="K67" s="27"/>
-      <c r="L67" s="27"/>
-      <c r="M67" s="27"/>
-      <c r="N67" s="27"/>
-      <c r="O67" s="27"/>
-      <c r="P67" s="27"/>
-      <c r="Q67" s="27"/>
-      <c r="R67" s="27"/>
-      <c r="S67" s="27"/>
-      <c r="T67" s="27"/>
-      <c r="U67" s="27"/>
-      <c r="V67" s="27"/>
-      <c r="W67" s="27"/>
-      <c r="X67" s="27"/>
-      <c r="Y67" s="27"/>
-      <c r="Z67" s="27"/>
-      <c r="AA67" s="27"/>
-      <c r="AB67" s="27"/>
-      <c r="AC67" s="27"/>
+      <c r="A67" s="27" t="s">
+        <v>485</v>
+      </c>
+      <c r="B67" s="28"/>
+      <c r="C67" s="28"/>
+      <c r="D67" s="28"/>
+      <c r="E67" s="28"/>
+      <c r="F67" s="28"/>
+      <c r="G67" s="28"/>
+      <c r="H67" s="28"/>
+      <c r="I67" s="28"/>
+      <c r="J67" s="28"/>
+      <c r="K67" s="28"/>
+      <c r="L67" s="28"/>
+      <c r="M67" s="28"/>
+      <c r="N67" s="28"/>
+      <c r="O67" s="28"/>
+      <c r="P67" s="28"/>
+      <c r="Q67" s="28"/>
+      <c r="R67" s="28"/>
+      <c r="S67" s="28"/>
+      <c r="T67" s="28"/>
+      <c r="U67" s="28"/>
+      <c r="V67" s="28"/>
+      <c r="W67" s="28"/>
+      <c r="X67" s="28"/>
+      <c r="Y67" s="28"/>
+      <c r="Z67" s="28"/>
+      <c r="AA67" s="28"/>
+      <c r="AB67" s="28"/>
+      <c r="AC67" s="28"/>
     </row>
     <row r="68" ht="15.0" customHeight="1">
-      <c r="A68" s="28" t="s">
-        <v>485</v>
-      </c>
-      <c r="B68" s="31">
+      <c r="A68" s="29" t="s">
+        <v>486</v>
+      </c>
+      <c r="B68" s="32">
         <v>10.93</v>
       </c>
-      <c r="C68" s="31">
+      <c r="C68" s="32">
         <v>14.15</v>
       </c>
-      <c r="D68" s="31">
+      <c r="D68" s="32">
         <v>26.83</v>
       </c>
-      <c r="E68" s="31">
+      <c r="E68" s="32">
         <v>11.21</v>
       </c>
-      <c r="F68" s="31">
+      <c r="F68" s="32">
         <v>4.99</v>
       </c>
-      <c r="G68" s="31">
+      <c r="G68" s="32">
         <v>13.02</v>
       </c>
-      <c r="H68" s="31">
+      <c r="H68" s="32">
         <v>11.76</v>
       </c>
-      <c r="I68" s="31">
+      <c r="I68" s="32">
         <v>9.8</v>
       </c>
-      <c r="J68" s="31">
+      <c r="J68" s="32">
         <v>8.62</v>
       </c>
-      <c r="K68" s="31">
+      <c r="K68" s="32">
         <v>11.32</v>
       </c>
-      <c r="L68" s="31">
+      <c r="L68" s="32">
         <v>4.52</v>
       </c>
-      <c r="M68" s="31">
+      <c r="M68" s="32">
         <v>12.99</v>
       </c>
-      <c r="N68" s="31">
+      <c r="N68" s="32">
         <v>4.34</v>
       </c>
-      <c r="O68" s="31">
+      <c r="O68" s="32">
         <v>3.29</v>
       </c>
-      <c r="P68" s="31">
+      <c r="P68" s="32">
         <v>34.77</v>
       </c>
-      <c r="Q68" s="31">
+      <c r="Q68" s="32">
         <v>3.47</v>
       </c>
-      <c r="R68" s="31">
+      <c r="R68" s="32">
         <v>2.85</v>
       </c>
-      <c r="S68" s="29"/>
-      <c r="T68" s="31">
+      <c r="S68" s="30"/>
+      <c r="T68" s="32">
         <v>5.99</v>
       </c>
-      <c r="U68" s="31">
+      <c r="U68" s="32">
         <v>19.72</v>
       </c>
-      <c r="V68" s="31">
+      <c r="V68" s="32">
         <v>9.77</v>
       </c>
-      <c r="W68" s="31">
+      <c r="W68" s="32">
         <v>7.72</v>
       </c>
-      <c r="X68" s="31">
+      <c r="X68" s="32">
         <v>6.65</v>
       </c>
-      <c r="Y68" s="31">
+      <c r="Y68" s="32">
         <v>3.63</v>
       </c>
-      <c r="Z68" s="29"/>
-      <c r="AA68" s="31">
+      <c r="Z68" s="30"/>
+      <c r="AA68" s="32">
         <v>4.84</v>
       </c>
-      <c r="AB68" s="29"/>
-      <c r="AC68" s="31">
+      <c r="AB68" s="30"/>
+      <c r="AC68" s="32">
         <v>12.33</v>
       </c>
     </row>
     <row r="69" ht="15.0" customHeight="1">
-      <c r="A69" s="28" t="s">
-        <v>486</v>
-      </c>
-      <c r="B69" s="31">
+      <c r="A69" s="29" t="s">
+        <v>487</v>
+      </c>
+      <c r="B69" s="32">
         <v>10.69</v>
       </c>
-      <c r="C69" s="31">
+      <c r="C69" s="32">
         <v>11.01</v>
       </c>
-      <c r="D69" s="31">
+      <c r="D69" s="32">
         <v>10.51</v>
       </c>
-      <c r="E69" s="31">
+      <c r="E69" s="32">
         <v>9.18</v>
       </c>
-      <c r="F69" s="31">
+      <c r="F69" s="32">
         <v>8.61</v>
       </c>
-      <c r="G69" s="31">
+      <c r="G69" s="32">
         <v>10.77</v>
       </c>
-      <c r="H69" s="31">
+      <c r="H69" s="32">
         <v>8.95</v>
       </c>
-      <c r="I69" s="31">
+      <c r="I69" s="32">
         <v>8.65</v>
       </c>
-      <c r="J69" s="31">
+      <c r="J69" s="32">
         <v>7.76</v>
       </c>
-      <c r="K69" s="31">
+      <c r="K69" s="32">
         <v>6.56</v>
       </c>
-      <c r="L69" s="31">
+      <c r="L69" s="32">
         <v>6.01</v>
       </c>
-      <c r="M69" s="31">
+      <c r="M69" s="32">
         <v>6.29</v>
       </c>
-      <c r="N69" s="31">
+      <c r="N69" s="32">
         <v>4.79</v>
       </c>
-      <c r="O69" s="31">
+      <c r="O69" s="32">
         <v>8.24</v>
       </c>
-      <c r="P69" s="31">
+      <c r="P69" s="32">
         <v>10.9</v>
       </c>
-      <c r="Q69" s="31">
+      <c r="Q69" s="32">
         <v>10.31</v>
       </c>
-      <c r="R69" s="31">
+      <c r="R69" s="32">
         <v>13.91</v>
       </c>
-      <c r="S69" s="31">
+      <c r="S69" s="32">
         <v>15.37</v>
       </c>
-      <c r="T69" s="31">
+      <c r="T69" s="32">
         <v>8.37</v>
       </c>
-      <c r="U69" s="31">
+      <c r="U69" s="32">
         <v>6.95</v>
       </c>
-      <c r="V69" s="31">
+      <c r="V69" s="32">
         <v>8.08</v>
       </c>
-      <c r="W69" s="31">
+      <c r="W69" s="32">
         <v>6.89</v>
       </c>
-      <c r="X69" s="31">
+      <c r="X69" s="32">
         <v>8.69</v>
       </c>
-      <c r="Y69" s="31">
+      <c r="Y69" s="32">
         <v>9.98</v>
       </c>
-      <c r="Z69" s="29"/>
-      <c r="AA69" s="29"/>
-      <c r="AB69" s="29"/>
-      <c r="AC69" s="29"/>
+      <c r="Z69" s="30"/>
+      <c r="AA69" s="30"/>
+      <c r="AB69" s="30"/>
+      <c r="AC69" s="30"/>
     </row>
     <row r="70" ht="15.0" customHeight="1">
-      <c r="A70" s="26" t="s">
-        <v>487</v>
-      </c>
-      <c r="B70" s="27"/>
-      <c r="C70" s="27"/>
-      <c r="D70" s="27"/>
-      <c r="E70" s="27"/>
-      <c r="F70" s="27"/>
-      <c r="G70" s="27"/>
-      <c r="H70" s="27"/>
-      <c r="I70" s="27"/>
-      <c r="J70" s="27"/>
-      <c r="K70" s="27"/>
-      <c r="L70" s="27"/>
-      <c r="M70" s="27"/>
-      <c r="N70" s="27"/>
-      <c r="O70" s="27"/>
-      <c r="P70" s="27"/>
-      <c r="Q70" s="27"/>
-      <c r="R70" s="27"/>
-      <c r="S70" s="27"/>
-      <c r="T70" s="27"/>
-      <c r="U70" s="27"/>
-      <c r="V70" s="27"/>
-      <c r="W70" s="27"/>
-      <c r="X70" s="27"/>
-      <c r="Y70" s="27"/>
-      <c r="Z70" s="27"/>
-      <c r="AA70" s="27"/>
-      <c r="AB70" s="27"/>
-      <c r="AC70" s="27"/>
+      <c r="A70" s="27" t="s">
+        <v>488</v>
+      </c>
+      <c r="B70" s="28"/>
+      <c r="C70" s="28"/>
+      <c r="D70" s="28"/>
+      <c r="E70" s="28"/>
+      <c r="F70" s="28"/>
+      <c r="G70" s="28"/>
+      <c r="H70" s="28"/>
+      <c r="I70" s="28"/>
+      <c r="J70" s="28"/>
+      <c r="K70" s="28"/>
+      <c r="L70" s="28"/>
+      <c r="M70" s="28"/>
+      <c r="N70" s="28"/>
+      <c r="O70" s="28"/>
+      <c r="P70" s="28"/>
+      <c r="Q70" s="28"/>
+      <c r="R70" s="28"/>
+      <c r="S70" s="28"/>
+      <c r="T70" s="28"/>
+      <c r="U70" s="28"/>
+      <c r="V70" s="28"/>
+      <c r="W70" s="28"/>
+      <c r="X70" s="28"/>
+      <c r="Y70" s="28"/>
+      <c r="Z70" s="28"/>
+      <c r="AA70" s="28"/>
+      <c r="AB70" s="28"/>
+      <c r="AC70" s="28"/>
     </row>
     <row r="71" ht="15.0" customHeight="1">
-      <c r="A71" s="28" t="s">
-        <v>488</v>
-      </c>
-      <c r="B71" s="31">
+      <c r="A71" s="29" t="s">
+        <v>489</v>
+      </c>
+      <c r="B71" s="32">
         <v>67.12</v>
       </c>
-      <c r="C71" s="29"/>
-      <c r="D71" s="29"/>
-      <c r="E71" s="31">
+      <c r="C71" s="30"/>
+      <c r="D71" s="30"/>
+      <c r="E71" s="32">
         <v>30.52</v>
       </c>
-      <c r="F71" s="31">
+      <c r="F71" s="32">
         <v>9.94</v>
       </c>
-      <c r="G71" s="29"/>
-      <c r="H71" s="29"/>
-      <c r="I71" s="29"/>
-      <c r="J71" s="29"/>
-      <c r="K71" s="29"/>
-      <c r="L71" s="31">
+      <c r="G71" s="30"/>
+      <c r="H71" s="30"/>
+      <c r="I71" s="30"/>
+      <c r="J71" s="30"/>
+      <c r="K71" s="30"/>
+      <c r="L71" s="32">
         <v>93.55</v>
       </c>
-      <c r="M71" s="29"/>
-      <c r="N71" s="31">
+      <c r="M71" s="30"/>
+      <c r="N71" s="32">
         <v>42.59</v>
       </c>
-      <c r="O71" s="31">
+      <c r="O71" s="32">
         <v>5.56</v>
       </c>
-      <c r="P71" s="29"/>
-      <c r="Q71" s="31">
+      <c r="P71" s="30"/>
+      <c r="Q71" s="32">
         <v>3.47</v>
       </c>
-      <c r="R71" s="31">
+      <c r="R71" s="32">
         <v>3.26</v>
       </c>
-      <c r="S71" s="29"/>
-      <c r="T71" s="31">
+      <c r="S71" s="30"/>
+      <c r="T71" s="32">
         <v>15.62</v>
       </c>
-      <c r="U71" s="29"/>
-      <c r="V71" s="29"/>
-      <c r="W71" s="31">
+      <c r="U71" s="30"/>
+      <c r="V71" s="30"/>
+      <c r="W71" s="32">
         <v>28.86</v>
       </c>
-      <c r="X71" s="31">
+      <c r="X71" s="32">
         <v>24.62</v>
       </c>
-      <c r="Y71" s="31">
+      <c r="Y71" s="32">
         <v>5.19</v>
       </c>
-      <c r="Z71" s="29"/>
-      <c r="AA71" s="31">
+      <c r="Z71" s="30"/>
+      <c r="AA71" s="32">
         <v>7.34</v>
       </c>
-      <c r="AB71" s="29"/>
-      <c r="AC71" s="31">
+      <c r="AB71" s="30"/>
+      <c r="AC71" s="32">
         <v>18.79</v>
       </c>
     </row>
     <row r="72" ht="15.0" customHeight="1">
-      <c r="A72" s="28" t="s">
-        <v>489</v>
-      </c>
-      <c r="B72" s="31">
+      <c r="A72" s="29" t="s">
+        <v>490</v>
+      </c>
+      <c r="B72" s="32">
         <v>78.54</v>
       </c>
-      <c r="C72" s="30">
+      <c r="C72" s="31">
         <v>201.18</v>
       </c>
-      <c r="D72" s="30">
+      <c r="D72" s="31">
         <v>225.36</v>
       </c>
-      <c r="E72" s="30">
+      <c r="E72" s="31">
         <v>129.55</v>
       </c>
-      <c r="F72" s="29"/>
-      <c r="G72" s="29"/>
-      <c r="H72" s="29"/>
-      <c r="I72" s="29"/>
-      <c r="J72" s="29"/>
-      <c r="K72" s="29"/>
-      <c r="L72" s="30">
+      <c r="F72" s="30"/>
+      <c r="G72" s="30"/>
+      <c r="H72" s="30"/>
+      <c r="I72" s="30"/>
+      <c r="J72" s="30"/>
+      <c r="K72" s="30"/>
+      <c r="L72" s="31">
         <v>533.35</v>
       </c>
-      <c r="M72" s="31">
+      <c r="M72" s="32">
         <v>32.26</v>
       </c>
-      <c r="N72" s="31">
+      <c r="N72" s="32">
         <v>9.65</v>
       </c>
-      <c r="O72" s="29"/>
-      <c r="P72" s="29"/>
-      <c r="Q72" s="29"/>
-      <c r="R72" s="29"/>
-      <c r="S72" s="29"/>
-      <c r="T72" s="31">
+      <c r="O72" s="30"/>
+      <c r="P72" s="30"/>
+      <c r="Q72" s="30"/>
+      <c r="R72" s="30"/>
+      <c r="S72" s="30"/>
+      <c r="T72" s="32">
         <v>46.74</v>
       </c>
-      <c r="U72" s="31">
+      <c r="U72" s="32">
         <v>20.12</v>
       </c>
-      <c r="V72" s="31">
+      <c r="V72" s="32">
         <v>34.46</v>
       </c>
-      <c r="W72" s="31">
+      <c r="W72" s="32">
         <v>17.15</v>
       </c>
-      <c r="X72" s="31">
+      <c r="X72" s="32">
         <v>28.18</v>
       </c>
-      <c r="Y72" s="31">
+      <c r="Y72" s="32">
         <v>25.86</v>
       </c>
-      <c r="Z72" s="29"/>
-      <c r="AA72" s="29"/>
-      <c r="AB72" s="29"/>
-      <c r="AC72" s="29"/>
+      <c r="Z72" s="30"/>
+      <c r="AA72" s="30"/>
+      <c r="AB72" s="30"/>
+      <c r="AC72" s="30"/>
     </row>
     <row r="73" ht="15.75" customHeight="1"/>
     <row r="74" ht="15.75" customHeight="1"/>
